--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$294</definedName>
     <definedName name="hostsex">'cv_sample'!$BM$1:$BM$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$R$1:$R$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AA$1:$AA$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DA$1:$DA$4</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="853">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1222,7 +1228,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -1450,9 +1456,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1471,6 +1474,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1672,6 +1678,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1681,9 +1690,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1723,7 +1729,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1792,6 +1798,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1867,6 +1876,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1888,6 +1900,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1933,6 +1948,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1945,6 +1963,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1954,9 +1975,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1981,6 +1999,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2041,12 +2062,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2167,13 +2188,13 @@
     <t>host height</t>
   </si>
   <si>
-    <t>(Optional) The height of subject (Units: mm)</t>
+    <t>(Optional) The height of subject (Units: m)</t>
   </si>
   <si>
     <t>host length</t>
   </si>
   <si>
-    <t>(Optional) The length of subject (Units: mm)</t>
+    <t>(Optional) The length of subject (Units: m)</t>
   </si>
   <si>
     <t>host growth conditions</t>
@@ -2263,7 +2284,7 @@
     <t>duration of association with the host</t>
   </si>
   <si>
-    <t>(Optional) Time spent in host of the symbiotic organism at the time of sampling; relevant scale depends on symbiotic organism and study. (Units: year)</t>
+    <t>(Optional) Time spent in host of the symbiotic organism at the time of sampling; relevant scale depends on symbiotic organism and study. (Units: minute)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2371,13 +2392,13 @@
     <t>host of the symbiotic host total mass</t>
   </si>
   <si>
-    <t>(Optional) Total mass of the host of the symbiotic host organism at collection, the unit depends on the host. (Units: µg)</t>
+    <t>(Optional) Total mass of the host of the symbiotic host organism at collection, the unit depends on the host. (Units: kg)</t>
   </si>
   <si>
     <t>host of the symbiotic host local environmental context</t>
   </si>
   <si>
-    <t>(Optional) For a symbiotic host organism the local anatomical environment within its host may have causal influences. report the anatomical entity(s) which are in the direct environment of the symbiotic host organism being sampled and which you believe have significant causal influences on your sample or specimen. for example, if the symbiotic host organism being sampled is an intestinal worm, its local environmental context will be the term for intestine from uberon (http://uberon.github.io/). (Units: g/m3)</t>
+    <t>(Optional) For a symbiotic host organism the local anatomical environment within its host may have causal influences. report the anatomical entity(s) which are in the direct environment of the symbiotic host organism being sampled and which you believe have significant causal influences on your sample or specimen. for example, if the symbiotic host organism being sampled is an intestinal worm, its local environmental context will be the term for intestine from uberon (http://uberon.github.io/). (Units: %)</t>
   </si>
   <si>
     <t>host of the symbiotic host common name</t>
@@ -2401,7 +2422,7 @@
     <t>host dry mass</t>
   </si>
   <si>
-    <t>(Optional) Measurement of dry mass (Units: mg)</t>
+    <t>(Optional) Measurement of dry mass (Units: kg)</t>
   </si>
   <si>
     <t>host body product</t>
@@ -2509,7 +2530,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2569,7 +2590,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Recommended) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>chemical administration</t>
@@ -3102,10 +3123,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3146,10 +3167,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +3197,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3193,7 +3214,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3210,7 +3231,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3227,7 +3248,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3244,7 +3265,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3261,7 +3282,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3278,7 +3299,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3295,7 +3316,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3312,7 +3333,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3329,7 +3350,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3343,7 +3364,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3357,7 +3378,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3371,7 +3392,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3385,7 +3406,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3399,7 +3420,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3413,7 +3434,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3427,7 +3448,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3441,7 +3462,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3451,8 +3472,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3463,7 +3487,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3474,7 +3498,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3485,7 +3509,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3496,7 +3520,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3507,7 +3531,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3518,7 +3542,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3529,7 +3553,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3540,7 +3564,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3551,7 +3575,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3562,7 +3586,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3573,7 +3597,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3584,7 +3608,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3595,7 +3619,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3603,7 +3627,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3611,7 +3635,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3619,7 +3643,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3627,7 +3651,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3635,7 +3659,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3643,7 +3667,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3651,7 +3675,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3659,7 +3683,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3675,236 +3699,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3926,27 +3955,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3966,122 +3995,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4105,714 +4134,714 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:119" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -4851,249 +4880,249 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:DA289"/>
+  <dimension ref="G1:DA294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:105">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="R1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AE1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AS1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BM1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="DA1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="2" spans="7:105">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AE2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AS2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BM2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="DA2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="7:105">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AS3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BM3" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="DA3" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="4" spans="7:105">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AS4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BM4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="DA4" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5" spans="7:105">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AS5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BM5" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="7:105">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AS6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BM6" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="7:105">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AS7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BM7" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8" spans="7:105">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AS8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BM8" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="7:105">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AS9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BM9" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="7:105">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AS10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="BM10" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="7:105">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AS11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="BM11" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" spans="7:105">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AS12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BM12" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="7:105">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AS13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BM13" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="14" spans="7:105">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AS14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="BM14" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" spans="7:105">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AS15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BM15" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="16" spans="7:105">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AS16" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BM16" t="s">
         <v>116</v>
@@ -5101,1412 +5130,1437 @@
     </row>
     <row r="17" spans="7:65">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AS17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="BM17" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" spans="7:65">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AS18" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="7:65">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AS19" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="7:65">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AS20" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="7:65">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AS21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="7:65">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AS22" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="7:65">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AS23" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="7:65">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AS24" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="7:65">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AS25" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="7:65">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AS26" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="7:65">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AS27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="7:65">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AS28" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="7:65">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AS29" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="7:65">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AS30" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" spans="7:65">
       <c r="AS31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="7:65">
       <c r="AS32" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="45:45">
       <c r="AS33" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="45:45">
       <c r="AS34" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="45:45">
       <c r="AS35" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="45:45">
       <c r="AS36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="45:45">
       <c r="AS37" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="45:45">
       <c r="AS38" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="45:45">
       <c r="AS39" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="40" spans="45:45">
       <c r="AS40" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="41" spans="45:45">
       <c r="AS41" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="42" spans="45:45">
       <c r="AS42" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" spans="45:45">
       <c r="AS43" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="45:45">
       <c r="AS44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="45:45">
       <c r="AS45" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="45:45">
       <c r="AS46" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="45:45">
       <c r="AS47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="45:45">
       <c r="AS48" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="45:45">
       <c r="AS49" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="50" spans="45:45">
       <c r="AS50" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51" spans="45:45">
       <c r="AS51" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="45:45">
       <c r="AS52" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="45:45">
       <c r="AS53" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54" spans="45:45">
       <c r="AS54" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" spans="45:45">
       <c r="AS55" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="45:45">
       <c r="AS56" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="45:45">
       <c r="AS57" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" spans="45:45">
       <c r="AS58" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="45:45">
       <c r="AS59" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" spans="45:45">
       <c r="AS60" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" spans="45:45">
       <c r="AS61" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="45:45">
       <c r="AS62" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="63" spans="45:45">
       <c r="AS63" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="45:45">
       <c r="AS64" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" spans="45:45">
       <c r="AS65" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="45:45">
       <c r="AS66" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="67" spans="45:45">
       <c r="AS67" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="45:45">
       <c r="AS68" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="45:45">
       <c r="AS69" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" spans="45:45">
       <c r="AS70" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="45:45">
       <c r="AS71" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="72" spans="45:45">
       <c r="AS72" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="73" spans="45:45">
       <c r="AS73" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="74" spans="45:45">
       <c r="AS74" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="45:45">
       <c r="AS75" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="76" spans="45:45">
       <c r="AS76" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="77" spans="45:45">
       <c r="AS77" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="78" spans="45:45">
       <c r="AS78" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79" spans="45:45">
       <c r="AS79" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="80" spans="45:45">
       <c r="AS80" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81" spans="45:45">
       <c r="AS81" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="82" spans="45:45">
       <c r="AS82" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="83" spans="45:45">
       <c r="AS83" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="84" spans="45:45">
       <c r="AS84" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85" spans="45:45">
       <c r="AS85" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="86" spans="45:45">
       <c r="AS86" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="45:45">
       <c r="AS87" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="88" spans="45:45">
       <c r="AS88" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="89" spans="45:45">
       <c r="AS89" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" spans="45:45">
       <c r="AS90" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="91" spans="45:45">
       <c r="AS91" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="92" spans="45:45">
       <c r="AS92" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="93" spans="45:45">
       <c r="AS93" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="94" spans="45:45">
       <c r="AS94" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="95" spans="45:45">
       <c r="AS95" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="96" spans="45:45">
       <c r="AS96" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="97" spans="45:45">
       <c r="AS97" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="98" spans="45:45">
       <c r="AS98" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="99" spans="45:45">
       <c r="AS99" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="45:45">
       <c r="AS100" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="45:45">
       <c r="AS101" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="102" spans="45:45">
       <c r="AS102" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="103" spans="45:45">
       <c r="AS103" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104" spans="45:45">
       <c r="AS104" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="105" spans="45:45">
       <c r="AS105" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="45:45">
       <c r="AS106" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="107" spans="45:45">
       <c r="AS107" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="108" spans="45:45">
       <c r="AS108" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" spans="45:45">
       <c r="AS109" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="110" spans="45:45">
       <c r="AS110" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" spans="45:45">
       <c r="AS111" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="112" spans="45:45">
       <c r="AS112" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="113" spans="45:45">
       <c r="AS113" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="114" spans="45:45">
       <c r="AS114" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="115" spans="45:45">
       <c r="AS115" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="116" spans="45:45">
       <c r="AS116" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="117" spans="45:45">
       <c r="AS117" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="118" spans="45:45">
       <c r="AS118" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="119" spans="45:45">
       <c r="AS119" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="120" spans="45:45">
       <c r="AS120" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="121" spans="45:45">
       <c r="AS121" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="122" spans="45:45">
       <c r="AS122" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="123" spans="45:45">
       <c r="AS123" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="124" spans="45:45">
       <c r="AS124" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="125" spans="45:45">
       <c r="AS125" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="126" spans="45:45">
       <c r="AS126" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="127" spans="45:45">
       <c r="AS127" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="128" spans="45:45">
       <c r="AS128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129" spans="45:45">
       <c r="AS129" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="130" spans="45:45">
       <c r="AS130" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="131" spans="45:45">
       <c r="AS131" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="132" spans="45:45">
       <c r="AS132" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="133" spans="45:45">
       <c r="AS133" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="134" spans="45:45">
       <c r="AS134" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="135" spans="45:45">
       <c r="AS135" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="136" spans="45:45">
       <c r="AS136" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="137" spans="45:45">
       <c r="AS137" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="45:45">
       <c r="AS138" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="139" spans="45:45">
       <c r="AS139" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="140" spans="45:45">
       <c r="AS140" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="141" spans="45:45">
       <c r="AS141" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="142" spans="45:45">
       <c r="AS142" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="143" spans="45:45">
       <c r="AS143" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="144" spans="45:45">
       <c r="AS144" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="145" spans="45:45">
       <c r="AS145" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" spans="45:45">
       <c r="AS146" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="147" spans="45:45">
       <c r="AS147" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="148" spans="45:45">
       <c r="AS148" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="149" spans="45:45">
       <c r="AS149" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="150" spans="45:45">
       <c r="AS150" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="151" spans="45:45">
       <c r="AS151" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="152" spans="45:45">
       <c r="AS152" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="45:45">
       <c r="AS153" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="154" spans="45:45">
       <c r="AS154" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="155" spans="45:45">
       <c r="AS155" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="156" spans="45:45">
       <c r="AS156" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="157" spans="45:45">
       <c r="AS157" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="158" spans="45:45">
       <c r="AS158" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="159" spans="45:45">
       <c r="AS159" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="160" spans="45:45">
       <c r="AS160" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="161" spans="45:45">
       <c r="AS161" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="162" spans="45:45">
       <c r="AS162" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="163" spans="45:45">
       <c r="AS163" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="164" spans="45:45">
       <c r="AS164" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="165" spans="45:45">
       <c r="AS165" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="166" spans="45:45">
       <c r="AS166" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="167" spans="45:45">
       <c r="AS167" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="168" spans="45:45">
       <c r="AS168" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="169" spans="45:45">
       <c r="AS169" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170" spans="45:45">
       <c r="AS170" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="171" spans="45:45">
       <c r="AS171" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="172" spans="45:45">
       <c r="AS172" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="173" spans="45:45">
       <c r="AS173" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="174" spans="45:45">
       <c r="AS174" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="175" spans="45:45">
       <c r="AS175" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="176" spans="45:45">
       <c r="AS176" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" spans="45:45">
       <c r="AS177" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="178" spans="45:45">
       <c r="AS178" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="179" spans="45:45">
       <c r="AS179" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="180" spans="45:45">
       <c r="AS180" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="181" spans="45:45">
       <c r="AS181" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="182" spans="45:45">
       <c r="AS182" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="183" spans="45:45">
       <c r="AS183" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="184" spans="45:45">
       <c r="AS184" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="185" spans="45:45">
       <c r="AS185" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="186" spans="45:45">
       <c r="AS186" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="187" spans="45:45">
       <c r="AS187" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="188" spans="45:45">
       <c r="AS188" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="189" spans="45:45">
       <c r="AS189" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="190" spans="45:45">
       <c r="AS190" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="191" spans="45:45">
       <c r="AS191" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="192" spans="45:45">
       <c r="AS192" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="193" spans="45:45">
       <c r="AS193" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="194" spans="45:45">
       <c r="AS194" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="195" spans="45:45">
       <c r="AS195" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="196" spans="45:45">
       <c r="AS196" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="197" spans="45:45">
       <c r="AS197" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="198" spans="45:45">
       <c r="AS198" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="199" spans="45:45">
       <c r="AS199" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="200" spans="45:45">
       <c r="AS200" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="201" spans="45:45">
       <c r="AS201" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="202" spans="45:45">
       <c r="AS202" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="203" spans="45:45">
       <c r="AS203" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="204" spans="45:45">
       <c r="AS204" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="205" spans="45:45">
       <c r="AS205" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="206" spans="45:45">
       <c r="AS206" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="207" spans="45:45">
       <c r="AS207" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="208" spans="45:45">
       <c r="AS208" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="209" spans="45:45">
       <c r="AS209" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="45:45">
       <c r="AS210" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="211" spans="45:45">
       <c r="AS211" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="212" spans="45:45">
       <c r="AS212" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="213" spans="45:45">
       <c r="AS213" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="214" spans="45:45">
       <c r="AS214" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="215" spans="45:45">
       <c r="AS215" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="216" spans="45:45">
       <c r="AS216" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="217" spans="45:45">
       <c r="AS217" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="218" spans="45:45">
       <c r="AS218" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="219" spans="45:45">
       <c r="AS219" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="220" spans="45:45">
       <c r="AS220" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="221" spans="45:45">
       <c r="AS221" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="222" spans="45:45">
       <c r="AS222" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="223" spans="45:45">
       <c r="AS223" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="224" spans="45:45">
       <c r="AS224" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="225" spans="45:45">
       <c r="AS225" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="226" spans="45:45">
       <c r="AS226" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="227" spans="45:45">
       <c r="AS227" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="228" spans="45:45">
       <c r="AS228" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="229" spans="45:45">
       <c r="AS229" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="230" spans="45:45">
       <c r="AS230" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="231" spans="45:45">
       <c r="AS231" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="232" spans="45:45">
       <c r="AS232" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="233" spans="45:45">
       <c r="AS233" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="234" spans="45:45">
       <c r="AS234" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="235" spans="45:45">
       <c r="AS235" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="236" spans="45:45">
       <c r="AS236" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="237" spans="45:45">
       <c r="AS237" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="238" spans="45:45">
       <c r="AS238" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="239" spans="45:45">
       <c r="AS239" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="240" spans="45:45">
       <c r="AS240" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="241" spans="45:45">
       <c r="AS241" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="242" spans="45:45">
       <c r="AS242" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="243" spans="45:45">
       <c r="AS243" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="244" spans="45:45">
       <c r="AS244" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="245" spans="45:45">
       <c r="AS245" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="246" spans="45:45">
       <c r="AS246" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="247" spans="45:45">
       <c r="AS247" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="248" spans="45:45">
       <c r="AS248" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="249" spans="45:45">
       <c r="AS249" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="250" spans="45:45">
       <c r="AS250" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="251" spans="45:45">
       <c r="AS251" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="252" spans="45:45">
       <c r="AS252" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="253" spans="45:45">
       <c r="AS253" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="254" spans="45:45">
       <c r="AS254" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="255" spans="45:45">
       <c r="AS255" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="256" spans="45:45">
       <c r="AS256" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="257" spans="45:45">
       <c r="AS257" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="258" spans="45:45">
       <c r="AS258" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="259" spans="45:45">
       <c r="AS259" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="260" spans="45:45">
       <c r="AS260" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="261" spans="45:45">
       <c r="AS261" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="262" spans="45:45">
       <c r="AS262" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="263" spans="45:45">
       <c r="AS263" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="264" spans="45:45">
       <c r="AS264" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="265" spans="45:45">
       <c r="AS265" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="266" spans="45:45">
       <c r="AS266" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="267" spans="45:45">
       <c r="AS267" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="268" spans="45:45">
       <c r="AS268" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="269" spans="45:45">
       <c r="AS269" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="270" spans="45:45">
       <c r="AS270" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="271" spans="45:45">
       <c r="AS271" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="272" spans="45:45">
       <c r="AS272" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="273" spans="45:45">
       <c r="AS273" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="274" spans="45:45">
       <c r="AS274" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="275" spans="45:45">
       <c r="AS275" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="276" spans="45:45">
       <c r="AS276" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="277" spans="45:45">
       <c r="AS277" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="278" spans="45:45">
       <c r="AS278" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="279" spans="45:45">
       <c r="AS279" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="280" spans="45:45">
       <c r="AS280" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="281" spans="45:45">
       <c r="AS281" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="282" spans="45:45">
       <c r="AS282" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="283" spans="45:45">
       <c r="AS283" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="284" spans="45:45">
       <c r="AS284" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="285" spans="45:45">
       <c r="AS285" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="286" spans="45:45">
       <c r="AS286" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="287" spans="45:45">
       <c r="AS287" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="288" spans="45:45">
       <c r="AS288" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="289" spans="45:45">
       <c r="AS289" t="s">
-        <v>687</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="290" spans="45:45">
+      <c r="AS290" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="291" spans="45:45">
+      <c r="AS291" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="292" spans="45:45">
+      <c r="AS292" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="293" spans="45:45">
+      <c r="AS293" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="294" spans="45:45">
+      <c r="AS294" t="s">
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -18,27 +18,27 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$289</definedName>
-    <definedName name="hostsex">'cv_sample'!$BK$1:$BK$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AR$1:$AR$294</definedName>
+    <definedName name="hostsex">'cv_sample'!$BL$1:$BL$17</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$P$1:$P$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$H$1:$H$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$Y$1:$Y$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$CY$1:$CY$4</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$Q$1:$Q$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$Z$1:$Z$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$CZ$1:$CZ$4</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$E$1:$E$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="851">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -844,6 +850,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1438,9 +1450,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1459,6 +1468,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1660,6 +1672,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1669,9 +1684,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1711,7 +1723,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1780,6 +1792,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1855,6 +1870,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1876,6 +1894,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1921,6 +1942,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1933,6 +1957,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1942,9 +1969,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1969,6 +1993,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2029,10 +2056,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3090,10 +3117,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3134,10 +3161,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3164,7 +3191,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3181,7 +3208,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3198,7 +3225,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3215,7 +3242,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3232,7 +3259,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3249,7 +3276,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3266,7 +3293,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3283,7 +3310,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3300,7 +3327,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3317,7 +3344,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3331,7 +3358,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3345,7 +3372,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3359,7 +3386,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3373,7 +3400,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3387,7 +3414,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3401,7 +3428,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3415,7 +3442,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3429,7 +3456,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3439,8 +3466,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3451,7 +3481,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3462,7 +3492,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3473,7 +3503,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3484,7 +3514,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3495,7 +3525,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3506,7 +3536,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3517,7 +3547,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3528,7 +3558,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3539,7 +3569,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3550,7 +3580,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3561,7 +3591,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3572,7 +3602,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3583,7 +3613,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3591,7 +3621,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3599,7 +3629,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3607,7 +3637,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3615,7 +3645,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3623,7 +3653,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3631,7 +3661,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3639,7 +3669,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3647,7 +3677,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3655,7 +3685,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3663,236 +3693,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3914,27 +3949,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3954,122 +3989,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4079,13 +4114,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DM2"/>
+  <dimension ref="A1:DN2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:117">
+    <row r="1" spans="1:118">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4093,731 +4128,737 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>684</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="2" spans="1:117" ht="150" customHeight="1">
+        <v>847</v>
+      </c>
+      <c r="DN1" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="2" spans="1:118" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>685</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
+      </c>
+      <c r="DN2" s="2" t="s">
+        <v>850</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK3:BK101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL101">
       <formula1>hostsex</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY3:CY101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ3:CZ101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -4827,1662 +4868,1687 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:CY289"/>
+  <dimension ref="F1:CZ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:103">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
+    <row r="1" spans="6:104">
       <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>369</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>399</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>733</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="2" spans="6:104">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>359</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>370</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>400</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>734</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="3" spans="6:104">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I3" t="s">
+        <v>317</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>360</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>401</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>735</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="4" spans="6:104">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>402</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>681</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="5" spans="6:104">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I5" t="s">
+        <v>319</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>403</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="6" spans="6:104">
+      <c r="F6" t="s">
+        <v>279</v>
+      </c>
+      <c r="I6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>404</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="7" spans="6:104">
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="I7" t="s">
+        <v>321</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>405</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="8" spans="6:104">
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>406</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="9" spans="6:104">
+      <c r="F9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>407</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="10" spans="6:104">
+      <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>408</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="11" spans="6:104">
+      <c r="F11" t="s">
+        <v>284</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>409</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="12" spans="6:104">
+      <c r="F12" t="s">
+        <v>285</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>410</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="13" spans="6:104">
+      <c r="F13" t="s">
+        <v>286</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>411</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="14" spans="6:104">
+      <c r="F14" t="s">
+        <v>287</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>412</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="15" spans="6:104">
+      <c r="F15" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>413</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="16" spans="6:104">
+      <c r="F16" t="s">
+        <v>289</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>414</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="6:64">
+      <c r="F17" t="s">
+        <v>290</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>415</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="18" spans="6:64">
+      <c r="F18" t="s">
+        <v>291</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="6:64">
+      <c r="F19" t="s">
+        <v>292</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="20" spans="6:64">
+      <c r="F20" t="s">
+        <v>293</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="21" spans="6:64">
+      <c r="F21" t="s">
+        <v>294</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="22" spans="6:64">
+      <c r="F22" t="s">
+        <v>295</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23" spans="6:64">
+      <c r="F23" t="s">
+        <v>296</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" spans="6:64">
+      <c r="F24" t="s">
+        <v>297</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="6:64">
+      <c r="F25" t="s">
+        <v>298</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="26" spans="6:64">
+      <c r="F26" t="s">
+        <v>299</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="27" spans="6:64">
+      <c r="F27" t="s">
+        <v>300</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28" spans="6:64">
+      <c r="F28" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="29" spans="6:64">
+      <c r="F29" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
-        <v>311</v>
-      </c>
-      <c r="P1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>354</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>365</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>395</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>724</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="2" spans="5:103">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="AR29" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="30" spans="6:64">
+      <c r="F30" t="s">
         <v>303</v>
       </c>
-      <c r="H2" t="s">
-        <v>312</v>
-      </c>
-      <c r="P2" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>355</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>366</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>396</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>725</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="3" spans="5:103">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" t="s">
-        <v>304</v>
-      </c>
-      <c r="H3" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>356</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>397</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>726</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="4" spans="5:103">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F4" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>398</v>
-      </c>
-      <c r="BK4" t="s">
+      <c r="AR30" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" spans="6:64">
+      <c r="AR31" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="32" spans="6:64">
+      <c r="AR32" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="33" spans="44:44">
+      <c r="AR33" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="44:44">
+      <c r="AR34" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="35" spans="44:44">
+      <c r="AR35" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="36" spans="44:44">
+      <c r="AR36" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="44:44">
+      <c r="AR37" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38" spans="44:44">
+      <c r="AR38" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="39" spans="44:44">
+      <c r="AR39" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="40" spans="44:44">
+      <c r="AR40" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="41" spans="44:44">
+      <c r="AR41" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="42" spans="44:44">
+      <c r="AR42" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="43" spans="44:44">
+      <c r="AR43" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="44" spans="44:44">
+      <c r="AR44" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="45" spans="44:44">
+      <c r="AR45" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="46" spans="44:44">
+      <c r="AR46" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="47" spans="44:44">
+      <c r="AR47" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="48" spans="44:44">
+      <c r="AR48" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="49" spans="44:44">
+      <c r="AR49" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="50" spans="44:44">
+      <c r="AR50" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="51" spans="44:44">
+      <c r="AR51" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="52" spans="44:44">
+      <c r="AR52" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="53" spans="44:44">
+      <c r="AR53" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="54" spans="44:44">
+      <c r="AR54" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="55" spans="44:44">
+      <c r="AR55" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="56" spans="44:44">
+      <c r="AR56" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="57" spans="44:44">
+      <c r="AR57" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="58" spans="44:44">
+      <c r="AR58" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="59" spans="44:44">
+      <c r="AR59" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="60" spans="44:44">
+      <c r="AR60" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="61" spans="44:44">
+      <c r="AR61" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="62" spans="44:44">
+      <c r="AR62" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="63" spans="44:44">
+      <c r="AR63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="44:44">
+      <c r="AR64" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="65" spans="44:44">
+      <c r="AR65" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="66" spans="44:44">
+      <c r="AR66" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="67" spans="44:44">
+      <c r="AR67" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="68" spans="44:44">
+      <c r="AR68" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="69" spans="44:44">
+      <c r="AR69" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="70" spans="44:44">
+      <c r="AR70" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="71" spans="44:44">
+      <c r="AR71" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="72" spans="44:44">
+      <c r="AR72" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="73" spans="44:44">
+      <c r="AR73" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="74" spans="44:44">
+      <c r="AR74" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="75" spans="44:44">
+      <c r="AR75" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="76" spans="44:44">
+      <c r="AR76" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="77" spans="44:44">
+      <c r="AR77" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="78" spans="44:44">
+      <c r="AR78" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="79" spans="44:44">
+      <c r="AR79" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="80" spans="44:44">
+      <c r="AR80" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="81" spans="44:44">
+      <c r="AR81" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="82" spans="44:44">
+      <c r="AR82" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="83" spans="44:44">
+      <c r="AR83" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="84" spans="44:44">
+      <c r="AR84" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="85" spans="44:44">
+      <c r="AR85" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="86" spans="44:44">
+      <c r="AR86" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="87" spans="44:44">
+      <c r="AR87" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="88" spans="44:44">
+      <c r="AR88" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="89" spans="44:44">
+      <c r="AR89" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="90" spans="44:44">
+      <c r="AR90" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="91" spans="44:44">
+      <c r="AR91" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="92" spans="44:44">
+      <c r="AR92" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="93" spans="44:44">
+      <c r="AR93" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="94" spans="44:44">
+      <c r="AR94" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="95" spans="44:44">
+      <c r="AR95" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="96" spans="44:44">
+      <c r="AR96" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="97" spans="44:44">
+      <c r="AR97" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="98" spans="44:44">
+      <c r="AR98" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="99" spans="44:44">
+      <c r="AR99" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="100" spans="44:44">
+      <c r="AR100" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="101" spans="44:44">
+      <c r="AR101" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="102" spans="44:44">
+      <c r="AR102" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="103" spans="44:44">
+      <c r="AR103" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="104" spans="44:44">
+      <c r="AR104" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="105" spans="44:44">
+      <c r="AR105" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="106" spans="44:44">
+      <c r="AR106" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="107" spans="44:44">
+      <c r="AR107" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="108" spans="44:44">
+      <c r="AR108" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="109" spans="44:44">
+      <c r="AR109" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="110" spans="44:44">
+      <c r="AR110" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="111" spans="44:44">
+      <c r="AR111" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="112" spans="44:44">
+      <c r="AR112" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="113" spans="44:44">
+      <c r="AR113" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="114" spans="44:44">
+      <c r="AR114" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="115" spans="44:44">
+      <c r="AR115" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="116" spans="44:44">
+      <c r="AR116" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="117" spans="44:44">
+      <c r="AR117" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="118" spans="44:44">
+      <c r="AR118" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="119" spans="44:44">
+      <c r="AR119" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="120" spans="44:44">
+      <c r="AR120" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="121" spans="44:44">
+      <c r="AR121" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="122" spans="44:44">
+      <c r="AR122" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="123" spans="44:44">
+      <c r="AR123" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="124" spans="44:44">
+      <c r="AR124" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="125" spans="44:44">
+      <c r="AR125" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="44:44">
+      <c r="AR126" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="127" spans="44:44">
+      <c r="AR127" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="128" spans="44:44">
+      <c r="AR128" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="129" spans="44:44">
+      <c r="AR129" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="130" spans="44:44">
+      <c r="AR130" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="131" spans="44:44">
+      <c r="AR131" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="132" spans="44:44">
+      <c r="AR132" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="133" spans="44:44">
+      <c r="AR133" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="134" spans="44:44">
+      <c r="AR134" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="135" spans="44:44">
+      <c r="AR135" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="136" spans="44:44">
+      <c r="AR136" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="137" spans="44:44">
+      <c r="AR137" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="138" spans="44:44">
+      <c r="AR138" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="139" spans="44:44">
+      <c r="AR139" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="140" spans="44:44">
+      <c r="AR140" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="141" spans="44:44">
+      <c r="AR141" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="142" spans="44:44">
+      <c r="AR142" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="143" spans="44:44">
+      <c r="AR143" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="144" spans="44:44">
+      <c r="AR144" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="145" spans="44:44">
+      <c r="AR145" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="146" spans="44:44">
+      <c r="AR146" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="147" spans="44:44">
+      <c r="AR147" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="148" spans="44:44">
+      <c r="AR148" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="149" spans="44:44">
+      <c r="AR149" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="150" spans="44:44">
+      <c r="AR150" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="151" spans="44:44">
+      <c r="AR151" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="152" spans="44:44">
+      <c r="AR152" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="153" spans="44:44">
+      <c r="AR153" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="154" spans="44:44">
+      <c r="AR154" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="155" spans="44:44">
+      <c r="AR155" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="156" spans="44:44">
+      <c r="AR156" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="157" spans="44:44">
+      <c r="AR157" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="158" spans="44:44">
+      <c r="AR158" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="159" spans="44:44">
+      <c r="AR159" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="160" spans="44:44">
+      <c r="AR160" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="161" spans="44:44">
+      <c r="AR161" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="162" spans="44:44">
+      <c r="AR162" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="163" spans="44:44">
+      <c r="AR163" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="164" spans="44:44">
+      <c r="AR164" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="165" spans="44:44">
+      <c r="AR165" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="166" spans="44:44">
+      <c r="AR166" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="167" spans="44:44">
+      <c r="AR167" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="168" spans="44:44">
+      <c r="AR168" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="169" spans="44:44">
+      <c r="AR169" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="170" spans="44:44">
+      <c r="AR170" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="171" spans="44:44">
+      <c r="AR171" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="172" spans="44:44">
+      <c r="AR172" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="173" spans="44:44">
+      <c r="AR173" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="174" spans="44:44">
+      <c r="AR174" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="175" spans="44:44">
+      <c r="AR175" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="176" spans="44:44">
+      <c r="AR176" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="177" spans="44:44">
+      <c r="AR177" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="178" spans="44:44">
+      <c r="AR178" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="179" spans="44:44">
+      <c r="AR179" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="180" spans="44:44">
+      <c r="AR180" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="181" spans="44:44">
+      <c r="AR181" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="182" spans="44:44">
+      <c r="AR182" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="183" spans="44:44">
+      <c r="AR183" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="184" spans="44:44">
+      <c r="AR184" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="185" spans="44:44">
+      <c r="AR185" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="186" spans="44:44">
+      <c r="AR186" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="187" spans="44:44">
+      <c r="AR187" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="188" spans="44:44">
+      <c r="AR188" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="189" spans="44:44">
+      <c r="AR189" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="190" spans="44:44">
+      <c r="AR190" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="191" spans="44:44">
+      <c r="AR191" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="192" spans="44:44">
+      <c r="AR192" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="193" spans="44:44">
+      <c r="AR193" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="194" spans="44:44">
+      <c r="AR194" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="195" spans="44:44">
+      <c r="AR195" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="196" spans="44:44">
+      <c r="AR196" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="197" spans="44:44">
+      <c r="AR197" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="198" spans="44:44">
+      <c r="AR198" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="199" spans="44:44">
+      <c r="AR199" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="200" spans="44:44">
+      <c r="AR200" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="201" spans="44:44">
+      <c r="AR201" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="202" spans="44:44">
+      <c r="AR202" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="203" spans="44:44">
+      <c r="AR203" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="204" spans="44:44">
+      <c r="AR204" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="205" spans="44:44">
+      <c r="AR205" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="206" spans="44:44">
+      <c r="AR206" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="207" spans="44:44">
+      <c r="AR207" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="208" spans="44:44">
+      <c r="AR208" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="209" spans="44:44">
+      <c r="AR209" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="210" spans="44:44">
+      <c r="AR210" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="211" spans="44:44">
+      <c r="AR211" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="212" spans="44:44">
+      <c r="AR212" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="213" spans="44:44">
+      <c r="AR213" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="214" spans="44:44">
+      <c r="AR214" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="215" spans="44:44">
+      <c r="AR215" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="216" spans="44:44">
+      <c r="AR216" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="217" spans="44:44">
+      <c r="AR217" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="218" spans="44:44">
+      <c r="AR218" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="219" spans="44:44">
+      <c r="AR219" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="220" spans="44:44">
+      <c r="AR220" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="221" spans="44:44">
+      <c r="AR221" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="222" spans="44:44">
+      <c r="AR222" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="223" spans="44:44">
+      <c r="AR223" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="224" spans="44:44">
+      <c r="AR224" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="225" spans="44:44">
+      <c r="AR225" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="226" spans="44:44">
+      <c r="AR226" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="227" spans="44:44">
+      <c r="AR227" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="228" spans="44:44">
+      <c r="AR228" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="229" spans="44:44">
+      <c r="AR229" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="230" spans="44:44">
+      <c r="AR230" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="231" spans="44:44">
+      <c r="AR231" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="232" spans="44:44">
+      <c r="AR232" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="233" spans="44:44">
+      <c r="AR233" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="234" spans="44:44">
+      <c r="AR234" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="235" spans="44:44">
+      <c r="AR235" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="236" spans="44:44">
+      <c r="AR236" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="237" spans="44:44">
+      <c r="AR237" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="238" spans="44:44">
+      <c r="AR238" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="239" spans="44:44">
+      <c r="AR239" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="240" spans="44:44">
+      <c r="AR240" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="241" spans="44:44">
+      <c r="AR241" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="242" spans="44:44">
+      <c r="AR242" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="243" spans="44:44">
+      <c r="AR243" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="244" spans="44:44">
+      <c r="AR244" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="245" spans="44:44">
+      <c r="AR245" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="246" spans="44:44">
+      <c r="AR246" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="247" spans="44:44">
+      <c r="AR247" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="248" spans="44:44">
+      <c r="AR248" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="249" spans="44:44">
+      <c r="AR249" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="250" spans="44:44">
+      <c r="AR250" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="251" spans="44:44">
+      <c r="AR251" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="252" spans="44:44">
+      <c r="AR252" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="253" spans="44:44">
+      <c r="AR253" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="254" spans="44:44">
+      <c r="AR254" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="255" spans="44:44">
+      <c r="AR255" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="256" spans="44:44">
+      <c r="AR256" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="257" spans="44:44">
+      <c r="AR257" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="258" spans="44:44">
+      <c r="AR258" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="259" spans="44:44">
+      <c r="AR259" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="260" spans="44:44">
+      <c r="AR260" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="261" spans="44:44">
+      <c r="AR261" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="262" spans="44:44">
+      <c r="AR262" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="263" spans="44:44">
+      <c r="AR263" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="264" spans="44:44">
+      <c r="AR264" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="265" spans="44:44">
+      <c r="AR265" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="266" spans="44:44">
+      <c r="AR266" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="267" spans="44:44">
+      <c r="AR267" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="268" spans="44:44">
+      <c r="AR268" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="269" spans="44:44">
+      <c r="AR269" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="270" spans="44:44">
+      <c r="AR270" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="271" spans="44:44">
+      <c r="AR271" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="272" spans="44:44">
+      <c r="AR272" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="273" spans="44:44">
+      <c r="AR273" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="274" spans="44:44">
+      <c r="AR274" t="s">
         <v>672</v>
       </c>
-      <c r="CY4" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="5" spans="5:103">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F5" t="s">
-        <v>306</v>
-      </c>
-      <c r="H5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>399</v>
-      </c>
-      <c r="BK5" t="s">
+    </row>
+    <row r="275" spans="44:44">
+      <c r="AR275" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="6" spans="5:103">
-      <c r="E6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H6" t="s">
-        <v>316</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>400</v>
-      </c>
-      <c r="BK6" t="s">
+    <row r="276" spans="44:44">
+      <c r="AR276" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="7" spans="5:103">
-      <c r="E7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H7" t="s">
-        <v>317</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>401</v>
-      </c>
-      <c r="BK7" t="s">
+    <row r="277" spans="44:44">
+      <c r="AR277" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="8" spans="5:103">
-      <c r="E8" t="s">
-        <v>277</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>402</v>
-      </c>
-      <c r="BK8" t="s">
+    <row r="278" spans="44:44">
+      <c r="AR278" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="9" spans="5:103">
-      <c r="E9" t="s">
-        <v>278</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>403</v>
-      </c>
-      <c r="BK9" t="s">
+    <row r="279" spans="44:44">
+      <c r="AR279" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="10" spans="5:103">
-      <c r="E10" t="s">
-        <v>279</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>404</v>
-      </c>
-      <c r="BK10" t="s">
+    <row r="280" spans="44:44">
+      <c r="AR280" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="11" spans="5:103">
-      <c r="E11" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>405</v>
-      </c>
-      <c r="BK11" t="s">
+    <row r="281" spans="44:44">
+      <c r="AR281" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="12" spans="5:103">
-      <c r="E12" t="s">
-        <v>281</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>406</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="13" spans="5:103">
-      <c r="E13" t="s">
-        <v>282</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>407</v>
-      </c>
-      <c r="BK13" t="s">
+    <row r="282" spans="44:44">
+      <c r="AR282" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="14" spans="5:103">
-      <c r="E14" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>408</v>
-      </c>
-      <c r="BK14" t="s">
+    <row r="283" spans="44:44">
+      <c r="AR283" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="15" spans="5:103">
-      <c r="E15" t="s">
-        <v>284</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>409</v>
-      </c>
-      <c r="BK15" t="s">
+    <row r="284" spans="44:44">
+      <c r="AR284" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="16" spans="5:103">
-      <c r="E16" t="s">
-        <v>285</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>410</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="5:63">
-      <c r="E17" t="s">
-        <v>286</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>411</v>
-      </c>
-      <c r="BK17" t="s">
+    <row r="285" spans="44:44">
+      <c r="AR285" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="18" spans="5:63">
-      <c r="E18" t="s">
-        <v>287</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="19" spans="5:63">
-      <c r="E19" t="s">
-        <v>288</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="20" spans="5:63">
-      <c r="E20" t="s">
-        <v>289</v>
-      </c>
-      <c r="AQ20" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="21" spans="5:63">
-      <c r="E21" t="s">
-        <v>290</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="22" spans="5:63">
-      <c r="E22" t="s">
-        <v>291</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="23" spans="5:63">
-      <c r="E23" t="s">
-        <v>292</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="24" spans="5:63">
-      <c r="E24" t="s">
-        <v>293</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="25" spans="5:63">
-      <c r="E25" t="s">
-        <v>294</v>
-      </c>
-      <c r="AQ25" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="26" spans="5:63">
-      <c r="E26" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="27" spans="5:63">
-      <c r="E27" t="s">
-        <v>296</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="28" spans="5:63">
-      <c r="E28" t="s">
-        <v>297</v>
-      </c>
-      <c r="AQ28" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="29" spans="5:63">
-      <c r="E29" t="s">
-        <v>298</v>
-      </c>
-      <c r="AQ29" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="30" spans="5:63">
-      <c r="E30" t="s">
-        <v>299</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="31" spans="5:63">
-      <c r="AQ31" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="32" spans="5:63">
-      <c r="AQ32" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="33" spans="43:43">
-      <c r="AQ33" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="34" spans="43:43">
-      <c r="AQ34" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="35" spans="43:43">
-      <c r="AQ35" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="36" spans="43:43">
-      <c r="AQ36" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="37" spans="43:43">
-      <c r="AQ37" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="38" spans="43:43">
-      <c r="AQ38" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="39" spans="43:43">
-      <c r="AQ39" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" spans="43:43">
-      <c r="AQ40" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="41" spans="43:43">
-      <c r="AQ41" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="42" spans="43:43">
-      <c r="AQ42" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="43" spans="43:43">
-      <c r="AQ43" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="44" spans="43:43">
-      <c r="AQ44" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="45" spans="43:43">
-      <c r="AQ45" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="46" spans="43:43">
-      <c r="AQ46" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="47" spans="43:43">
-      <c r="AQ47" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="48" spans="43:43">
-      <c r="AQ48" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="49" spans="43:43">
-      <c r="AQ49" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="50" spans="43:43">
-      <c r="AQ50" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="51" spans="43:43">
-      <c r="AQ51" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="52" spans="43:43">
-      <c r="AQ52" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="53" spans="43:43">
-      <c r="AQ53" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="54" spans="43:43">
-      <c r="AQ54" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="55" spans="43:43">
-      <c r="AQ55" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="56" spans="43:43">
-      <c r="AQ56" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="57" spans="43:43">
-      <c r="AQ57" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="58" spans="43:43">
-      <c r="AQ58" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="59" spans="43:43">
-      <c r="AQ59" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="60" spans="43:43">
-      <c r="AQ60" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="61" spans="43:43">
-      <c r="AQ61" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="62" spans="43:43">
-      <c r="AQ62" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="63" spans="43:43">
-      <c r="AQ63" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="64" spans="43:43">
-      <c r="AQ64" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="65" spans="43:43">
-      <c r="AQ65" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="66" spans="43:43">
-      <c r="AQ66" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="67" spans="43:43">
-      <c r="AQ67" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="68" spans="43:43">
-      <c r="AQ68" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="69" spans="43:43">
-      <c r="AQ69" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="70" spans="43:43">
-      <c r="AQ70" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="71" spans="43:43">
-      <c r="AQ71" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="72" spans="43:43">
-      <c r="AQ72" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="73" spans="43:43">
-      <c r="AQ73" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="74" spans="43:43">
-      <c r="AQ74" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="75" spans="43:43">
-      <c r="AQ75" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="76" spans="43:43">
-      <c r="AQ76" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="77" spans="43:43">
-      <c r="AQ77" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="78" spans="43:43">
-      <c r="AQ78" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="79" spans="43:43">
-      <c r="AQ79" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="80" spans="43:43">
-      <c r="AQ80" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="81" spans="43:43">
-      <c r="AQ81" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="82" spans="43:43">
-      <c r="AQ82" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="83" spans="43:43">
-      <c r="AQ83" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="84" spans="43:43">
-      <c r="AQ84" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="85" spans="43:43">
-      <c r="AQ85" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="86" spans="43:43">
-      <c r="AQ86" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="87" spans="43:43">
-      <c r="AQ87" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="88" spans="43:43">
-      <c r="AQ88" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="89" spans="43:43">
-      <c r="AQ89" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="90" spans="43:43">
-      <c r="AQ90" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="91" spans="43:43">
-      <c r="AQ91" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="92" spans="43:43">
-      <c r="AQ92" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="93" spans="43:43">
-      <c r="AQ93" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="94" spans="43:43">
-      <c r="AQ94" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="95" spans="43:43">
-      <c r="AQ95" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="96" spans="43:43">
-      <c r="AQ96" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="97" spans="43:43">
-      <c r="AQ97" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="98" spans="43:43">
-      <c r="AQ98" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="99" spans="43:43">
-      <c r="AQ99" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="100" spans="43:43">
-      <c r="AQ100" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="101" spans="43:43">
-      <c r="AQ101" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="102" spans="43:43">
-      <c r="AQ102" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="103" spans="43:43">
-      <c r="AQ103" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="104" spans="43:43">
-      <c r="AQ104" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="105" spans="43:43">
-      <c r="AQ105" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="106" spans="43:43">
-      <c r="AQ106" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" spans="43:43">
-      <c r="AQ107" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="108" spans="43:43">
-      <c r="AQ108" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="109" spans="43:43">
-      <c r="AQ109" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="110" spans="43:43">
-      <c r="AQ110" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="111" spans="43:43">
-      <c r="AQ111" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="112" spans="43:43">
-      <c r="AQ112" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="113" spans="43:43">
-      <c r="AQ113" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="114" spans="43:43">
-      <c r="AQ114" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="115" spans="43:43">
-      <c r="AQ115" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="116" spans="43:43">
-      <c r="AQ116" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="117" spans="43:43">
-      <c r="AQ117" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="118" spans="43:43">
-      <c r="AQ118" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="119" spans="43:43">
-      <c r="AQ119" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="120" spans="43:43">
-      <c r="AQ120" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="121" spans="43:43">
-      <c r="AQ121" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="122" spans="43:43">
-      <c r="AQ122" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="123" spans="43:43">
-      <c r="AQ123" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="124" spans="43:43">
-      <c r="AQ124" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="125" spans="43:43">
-      <c r="AQ125" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="126" spans="43:43">
-      <c r="AQ126" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="127" spans="43:43">
-      <c r="AQ127" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="128" spans="43:43">
-      <c r="AQ128" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="129" spans="43:43">
-      <c r="AQ129" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="130" spans="43:43">
-      <c r="AQ130" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="131" spans="43:43">
-      <c r="AQ131" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="132" spans="43:43">
-      <c r="AQ132" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="133" spans="43:43">
-      <c r="AQ133" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="134" spans="43:43">
-      <c r="AQ134" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="135" spans="43:43">
-      <c r="AQ135" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="136" spans="43:43">
-      <c r="AQ136" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="137" spans="43:43">
-      <c r="AQ137" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="138" spans="43:43">
-      <c r="AQ138" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="139" spans="43:43">
-      <c r="AQ139" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="140" spans="43:43">
-      <c r="AQ140" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="141" spans="43:43">
-      <c r="AQ141" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="142" spans="43:43">
-      <c r="AQ142" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="143" spans="43:43">
-      <c r="AQ143" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="144" spans="43:43">
-      <c r="AQ144" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="145" spans="43:43">
-      <c r="AQ145" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="146" spans="43:43">
-      <c r="AQ146" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="147" spans="43:43">
-      <c r="AQ147" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="148" spans="43:43">
-      <c r="AQ148" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="149" spans="43:43">
-      <c r="AQ149" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="150" spans="43:43">
-      <c r="AQ150" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="151" spans="43:43">
-      <c r="AQ151" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="152" spans="43:43">
-      <c r="AQ152" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="153" spans="43:43">
-      <c r="AQ153" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="154" spans="43:43">
-      <c r="AQ154" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="155" spans="43:43">
-      <c r="AQ155" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="156" spans="43:43">
-      <c r="AQ156" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="157" spans="43:43">
-      <c r="AQ157" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="158" spans="43:43">
-      <c r="AQ158" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="159" spans="43:43">
-      <c r="AQ159" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="160" spans="43:43">
-      <c r="AQ160" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="161" spans="43:43">
-      <c r="AQ161" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="162" spans="43:43">
-      <c r="AQ162" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="163" spans="43:43">
-      <c r="AQ163" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="164" spans="43:43">
-      <c r="AQ164" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="165" spans="43:43">
-      <c r="AQ165" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="166" spans="43:43">
-      <c r="AQ166" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="167" spans="43:43">
-      <c r="AQ167" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="168" spans="43:43">
-      <c r="AQ168" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="169" spans="43:43">
-      <c r="AQ169" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="170" spans="43:43">
-      <c r="AQ170" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="171" spans="43:43">
-      <c r="AQ171" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="172" spans="43:43">
-      <c r="AQ172" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="173" spans="43:43">
-      <c r="AQ173" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="174" spans="43:43">
-      <c r="AQ174" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="175" spans="43:43">
-      <c r="AQ175" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="176" spans="43:43">
-      <c r="AQ176" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="177" spans="43:43">
-      <c r="AQ177" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="178" spans="43:43">
-      <c r="AQ178" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="179" spans="43:43">
-      <c r="AQ179" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="180" spans="43:43">
-      <c r="AQ180" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="181" spans="43:43">
-      <c r="AQ181" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="182" spans="43:43">
-      <c r="AQ182" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="183" spans="43:43">
-      <c r="AQ183" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="184" spans="43:43">
-      <c r="AQ184" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="185" spans="43:43">
-      <c r="AQ185" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="186" spans="43:43">
-      <c r="AQ186" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="187" spans="43:43">
-      <c r="AQ187" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="188" spans="43:43">
-      <c r="AQ188" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="189" spans="43:43">
-      <c r="AQ189" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="190" spans="43:43">
-      <c r="AQ190" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="191" spans="43:43">
-      <c r="AQ191" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="192" spans="43:43">
-      <c r="AQ192" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="193" spans="43:43">
-      <c r="AQ193" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="194" spans="43:43">
-      <c r="AQ194" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="195" spans="43:43">
-      <c r="AQ195" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="196" spans="43:43">
-      <c r="AQ196" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="197" spans="43:43">
-      <c r="AQ197" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="198" spans="43:43">
-      <c r="AQ198" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="199" spans="43:43">
-      <c r="AQ199" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="200" spans="43:43">
-      <c r="AQ200" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="201" spans="43:43">
-      <c r="AQ201" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="202" spans="43:43">
-      <c r="AQ202" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="203" spans="43:43">
-      <c r="AQ203" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="204" spans="43:43">
-      <c r="AQ204" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="205" spans="43:43">
-      <c r="AQ205" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="206" spans="43:43">
-      <c r="AQ206" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="207" spans="43:43">
-      <c r="AQ207" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="208" spans="43:43">
-      <c r="AQ208" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="209" spans="43:43">
-      <c r="AQ209" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="210" spans="43:43">
-      <c r="AQ210" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="211" spans="43:43">
-      <c r="AQ211" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="212" spans="43:43">
-      <c r="AQ212" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="213" spans="43:43">
-      <c r="AQ213" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="214" spans="43:43">
-      <c r="AQ214" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="215" spans="43:43">
-      <c r="AQ215" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="216" spans="43:43">
-      <c r="AQ216" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="217" spans="43:43">
-      <c r="AQ217" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="218" spans="43:43">
-      <c r="AQ218" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="219" spans="43:43">
-      <c r="AQ219" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="220" spans="43:43">
-      <c r="AQ220" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="221" spans="43:43">
-      <c r="AQ221" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="222" spans="43:43">
-      <c r="AQ222" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="223" spans="43:43">
-      <c r="AQ223" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="224" spans="43:43">
-      <c r="AQ224" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="225" spans="43:43">
-      <c r="AQ225" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="226" spans="43:43">
-      <c r="AQ226" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="227" spans="43:43">
-      <c r="AQ227" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="228" spans="43:43">
-      <c r="AQ228" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="229" spans="43:43">
-      <c r="AQ229" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="230" spans="43:43">
-      <c r="AQ230" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="231" spans="43:43">
-      <c r="AQ231" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="232" spans="43:43">
-      <c r="AQ232" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="233" spans="43:43">
-      <c r="AQ233" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="234" spans="43:43">
-      <c r="AQ234" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="235" spans="43:43">
-      <c r="AQ235" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="236" spans="43:43">
-      <c r="AQ236" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="237" spans="43:43">
-      <c r="AQ237" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="238" spans="43:43">
-      <c r="AQ238" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="239" spans="43:43">
-      <c r="AQ239" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="240" spans="43:43">
-      <c r="AQ240" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="241" spans="43:43">
-      <c r="AQ241" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="242" spans="43:43">
-      <c r="AQ242" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="243" spans="43:43">
-      <c r="AQ243" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="244" spans="43:43">
-      <c r="AQ244" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="245" spans="43:43">
-      <c r="AQ245" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="246" spans="43:43">
-      <c r="AQ246" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="247" spans="43:43">
-      <c r="AQ247" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="248" spans="43:43">
-      <c r="AQ248" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="249" spans="43:43">
-      <c r="AQ249" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="250" spans="43:43">
-      <c r="AQ250" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="251" spans="43:43">
-      <c r="AQ251" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="252" spans="43:43">
-      <c r="AQ252" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="253" spans="43:43">
-      <c r="AQ253" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="254" spans="43:43">
-      <c r="AQ254" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="255" spans="43:43">
-      <c r="AQ255" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="256" spans="43:43">
-      <c r="AQ256" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="257" spans="43:43">
-      <c r="AQ257" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="258" spans="43:43">
-      <c r="AQ258" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="259" spans="43:43">
-      <c r="AQ259" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="260" spans="43:43">
-      <c r="AQ260" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="261" spans="43:43">
-      <c r="AQ261" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="262" spans="43:43">
-      <c r="AQ262" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="263" spans="43:43">
-      <c r="AQ263" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="264" spans="43:43">
-      <c r="AQ264" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="265" spans="43:43">
-      <c r="AQ265" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="266" spans="43:43">
-      <c r="AQ266" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="267" spans="43:43">
-      <c r="AQ267" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="268" spans="43:43">
-      <c r="AQ268" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="269" spans="43:43">
-      <c r="AQ269" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="270" spans="43:43">
-      <c r="AQ270" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="271" spans="43:43">
-      <c r="AQ271" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="272" spans="43:43">
-      <c r="AQ272" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="273" spans="43:43">
-      <c r="AQ273" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="274" spans="43:43">
-      <c r="AQ274" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="275" spans="43:43">
-      <c r="AQ275" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="276" spans="43:43">
-      <c r="AQ276" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="277" spans="43:43">
-      <c r="AQ277" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="278" spans="43:43">
-      <c r="AQ278" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="279" spans="43:43">
-      <c r="AQ279" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="280" spans="43:43">
-      <c r="AQ280" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="281" spans="43:43">
-      <c r="AQ281" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="282" spans="43:43">
-      <c r="AQ282" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="283" spans="43:43">
-      <c r="AQ283" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="284" spans="43:43">
-      <c r="AQ284" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="285" spans="43:43">
-      <c r="AQ285" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="286" spans="43:43">
-      <c r="AQ286" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="287" spans="43:43">
-      <c r="AQ287" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="288" spans="43:43">
-      <c r="AQ288" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="289" spans="43:43">
-      <c r="AQ289" t="s">
-        <v>683</v>
+    <row r="286" spans="44:44">
+      <c r="AR286" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="287" spans="44:44">
+      <c r="AR287" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="288" spans="44:44">
+      <c r="AR288" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="289" spans="44:44">
+      <c r="AR289" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="290" spans="44:44">
+      <c r="AR290" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="291" spans="44:44">
+      <c r="AR291" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="292" spans="44:44">
+      <c r="AR292" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="293" spans="44:44">
+      <c r="AR293" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="294" spans="44:44">
+      <c r="AR294" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -18,27 +18,27 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AR$1:$AR$294</definedName>
-    <definedName name="hostsex">'cv_sample'!$BL$1:$BL$17</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$294</definedName>
+    <definedName name="hostsex">'cv_sample'!$BM$1:$BM$17</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$Q$1:$Q$2</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$R$1:$R$2</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$I$1:$I$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$Z$1:$Z$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$CZ$1:$CZ$4</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AA$1:$AA$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DA$1:$DA$4</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$F$1:$F$30</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$G$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="853">
   <si>
     <t>alias</t>
   </si>
@@ -854,6 +854,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4114,13 +4120,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DN2"/>
+  <dimension ref="A1:DO2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118">
+    <row r="1" spans="1:119">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4137,16 +4143,16 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>324</v>
@@ -4170,7 +4176,7 @@
         <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>342</v>
@@ -4197,7 +4203,7 @@
         <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>363</v>
@@ -4209,7 +4215,7 @@
         <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>373</v>
@@ -4251,7 +4257,7 @@
         <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>693</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>695</v>
@@ -4311,7 +4317,7 @@
         <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>739</v>
@@ -4431,7 +4437,7 @@
         <v>815</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="DA1" s="1" t="s">
         <v>823</v>
@@ -4475,8 +4481,11 @@
       <c r="DN1" s="1" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="2" spans="1:118" ht="150" customHeight="1">
+      <c r="DO1" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="2" spans="1:119" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4493,16 +4502,16 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>325</v>
@@ -4526,7 +4535,7 @@
         <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>343</v>
@@ -4553,7 +4562,7 @@
         <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>364</v>
@@ -4565,7 +4574,7 @@
         <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>374</v>
@@ -4607,7 +4616,7 @@
         <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>694</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
         <v>696</v>
@@ -4667,7 +4676,7 @@
         <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
         <v>740</v>
@@ -4787,7 +4796,7 @@
         <v>816</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="DA2" s="2" t="s">
         <v>824</v>
@@ -4831,34 +4840,37 @@
       <c r="DN2" s="2" t="s">
         <v>850</v>
       </c>
+      <c r="DO2" s="2" t="s">
+        <v>852</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA3:AA101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR3:AR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM101">
       <formula1>hostsex</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ3:CZ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DA3:DA101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -4868,1687 +4880,1687 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:CZ294"/>
+  <dimension ref="G1:DA294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:104">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
+    <row r="1" spans="7:105">
       <c r="G1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>358</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>369</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>399</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>733</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="2" spans="6:104">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="R1" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>371</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>401</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>735</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="2" spans="7:105">
       <c r="G2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>339</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>359</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>400</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>734</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="3" spans="6:104">
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" t="s">
+        <v>318</v>
+      </c>
+      <c r="R2" t="s">
+        <v>341</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>361</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>372</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>402</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>736</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="3" spans="7:105">
       <c r="G3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I3" t="s">
-        <v>317</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>360</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>401</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>735</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="4" spans="6:104">
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J3" t="s">
+        <v>319</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>403</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>737</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="4" spans="7:105">
       <c r="G4" t="s">
-        <v>309</v>
-      </c>
-      <c r="I4" t="s">
-        <v>318</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>402</v>
-      </c>
-      <c r="BL4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" t="s">
+        <v>320</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>404</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>683</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="5" spans="7:105">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J5" t="s">
+        <v>321</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>405</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="6" spans="7:105">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>406</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="7" spans="7:105">
+      <c r="G7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>407</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="8" spans="7:105">
+      <c r="G8" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>408</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" spans="7:105">
+      <c r="G9" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>409</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="10" spans="7:105">
+      <c r="G10" t="s">
+        <v>285</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>410</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="11" spans="7:105">
+      <c r="G11" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>411</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="12" spans="7:105">
+      <c r="G12" t="s">
+        <v>287</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>412</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="7:105">
+      <c r="G13" t="s">
+        <v>288</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>413</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="14" spans="7:105">
+      <c r="G14" t="s">
+        <v>289</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>414</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="15" spans="7:105">
+      <c r="G15" t="s">
+        <v>290</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>415</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="16" spans="7:105">
+      <c r="G16" t="s">
+        <v>291</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>416</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="7:65">
+      <c r="G17" t="s">
+        <v>292</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>417</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="18" spans="7:65">
+      <c r="G18" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="7:65">
+      <c r="G19" t="s">
+        <v>294</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="20" spans="7:65">
+      <c r="G20" t="s">
+        <v>295</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="21" spans="7:65">
+      <c r="G21" t="s">
+        <v>296</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="22" spans="7:65">
+      <c r="G22" t="s">
+        <v>297</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="23" spans="7:65">
+      <c r="G23" t="s">
+        <v>298</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="24" spans="7:65">
+      <c r="G24" t="s">
+        <v>299</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="25" spans="7:65">
+      <c r="G25" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="26" spans="7:65">
+      <c r="G26" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="27" spans="7:65">
+      <c r="G27" t="s">
+        <v>302</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="28" spans="7:65">
+      <c r="G28" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" spans="7:65">
+      <c r="G29" t="s">
+        <v>304</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="30" spans="7:65">
+      <c r="G30" t="s">
+        <v>305</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="31" spans="7:65">
+      <c r="AS31" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" spans="7:65">
+      <c r="AS32" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="33" spans="45:45">
+      <c r="AS33" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="34" spans="45:45">
+      <c r="AS34" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="35" spans="45:45">
+      <c r="AS35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="45:45">
+      <c r="AS36" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="45:45">
+      <c r="AS37" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="38" spans="45:45">
+      <c r="AS38" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="39" spans="45:45">
+      <c r="AS39" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="40" spans="45:45">
+      <c r="AS40" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="41" spans="45:45">
+      <c r="AS41" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="42" spans="45:45">
+      <c r="AS42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="43" spans="45:45">
+      <c r="AS43" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="44" spans="45:45">
+      <c r="AS44" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="45" spans="45:45">
+      <c r="AS45" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="46" spans="45:45">
+      <c r="AS46" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="45:45">
+      <c r="AS47" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" spans="45:45">
+      <c r="AS48" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="49" spans="45:45">
+      <c r="AS49" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="50" spans="45:45">
+      <c r="AS50" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="51" spans="45:45">
+      <c r="AS51" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="52" spans="45:45">
+      <c r="AS52" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="53" spans="45:45">
+      <c r="AS53" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="54" spans="45:45">
+      <c r="AS54" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="55" spans="45:45">
+      <c r="AS55" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="56" spans="45:45">
+      <c r="AS56" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="57" spans="45:45">
+      <c r="AS57" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="58" spans="45:45">
+      <c r="AS58" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="59" spans="45:45">
+      <c r="AS59" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="60" spans="45:45">
+      <c r="AS60" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="61" spans="45:45">
+      <c r="AS61" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="62" spans="45:45">
+      <c r="AS62" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="63" spans="45:45">
+      <c r="AS63" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="45:45">
+      <c r="AS64" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="65" spans="45:45">
+      <c r="AS65" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="66" spans="45:45">
+      <c r="AS66" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="67" spans="45:45">
+      <c r="AS67" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="68" spans="45:45">
+      <c r="AS68" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69" spans="45:45">
+      <c r="AS69" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="70" spans="45:45">
+      <c r="AS70" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="71" spans="45:45">
+      <c r="AS71" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="72" spans="45:45">
+      <c r="AS72" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="73" spans="45:45">
+      <c r="AS73" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="74" spans="45:45">
+      <c r="AS74" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="75" spans="45:45">
+      <c r="AS75" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="76" spans="45:45">
+      <c r="AS76" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="77" spans="45:45">
+      <c r="AS77" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="78" spans="45:45">
+      <c r="AS78" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="79" spans="45:45">
+      <c r="AS79" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="80" spans="45:45">
+      <c r="AS80" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="81" spans="45:45">
+      <c r="AS81" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="82" spans="45:45">
+      <c r="AS82" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="83" spans="45:45">
+      <c r="AS83" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="84" spans="45:45">
+      <c r="AS84" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="85" spans="45:45">
+      <c r="AS85" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="86" spans="45:45">
+      <c r="AS86" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="87" spans="45:45">
+      <c r="AS87" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="88" spans="45:45">
+      <c r="AS88" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="89" spans="45:45">
+      <c r="AS89" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="90" spans="45:45">
+      <c r="AS90" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="91" spans="45:45">
+      <c r="AS91" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="92" spans="45:45">
+      <c r="AS92" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="93" spans="45:45">
+      <c r="AS93" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="94" spans="45:45">
+      <c r="AS94" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="95" spans="45:45">
+      <c r="AS95" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="96" spans="45:45">
+      <c r="AS96" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="97" spans="45:45">
+      <c r="AS97" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="98" spans="45:45">
+      <c r="AS98" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="99" spans="45:45">
+      <c r="AS99" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="100" spans="45:45">
+      <c r="AS100" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="101" spans="45:45">
+      <c r="AS101" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="102" spans="45:45">
+      <c r="AS102" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="103" spans="45:45">
+      <c r="AS103" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="45:45">
+      <c r="AS104" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="105" spans="45:45">
+      <c r="AS105" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="106" spans="45:45">
+      <c r="AS106" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="107" spans="45:45">
+      <c r="AS107" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="108" spans="45:45">
+      <c r="AS108" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="109" spans="45:45">
+      <c r="AS109" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="110" spans="45:45">
+      <c r="AS110" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="111" spans="45:45">
+      <c r="AS111" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="112" spans="45:45">
+      <c r="AS112" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="113" spans="45:45">
+      <c r="AS113" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="114" spans="45:45">
+      <c r="AS114" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="115" spans="45:45">
+      <c r="AS115" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="116" spans="45:45">
+      <c r="AS116" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="117" spans="45:45">
+      <c r="AS117" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="118" spans="45:45">
+      <c r="AS118" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="119" spans="45:45">
+      <c r="AS119" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="120" spans="45:45">
+      <c r="AS120" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="121" spans="45:45">
+      <c r="AS121" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="122" spans="45:45">
+      <c r="AS122" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="123" spans="45:45">
+      <c r="AS123" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="124" spans="45:45">
+      <c r="AS124" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="125" spans="45:45">
+      <c r="AS125" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="126" spans="45:45">
+      <c r="AS126" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="127" spans="45:45">
+      <c r="AS127" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="128" spans="45:45">
+      <c r="AS128" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="129" spans="45:45">
+      <c r="AS129" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="130" spans="45:45">
+      <c r="AS130" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="131" spans="45:45">
+      <c r="AS131" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="132" spans="45:45">
+      <c r="AS132" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="133" spans="45:45">
+      <c r="AS133" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="134" spans="45:45">
+      <c r="AS134" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="135" spans="45:45">
+      <c r="AS135" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="136" spans="45:45">
+      <c r="AS136" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="137" spans="45:45">
+      <c r="AS137" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="138" spans="45:45">
+      <c r="AS138" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="139" spans="45:45">
+      <c r="AS139" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="140" spans="45:45">
+      <c r="AS140" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="141" spans="45:45">
+      <c r="AS141" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="142" spans="45:45">
+      <c r="AS142" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="143" spans="45:45">
+      <c r="AS143" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="144" spans="45:45">
+      <c r="AS144" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="145" spans="45:45">
+      <c r="AS145" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="146" spans="45:45">
+      <c r="AS146" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="147" spans="45:45">
+      <c r="AS147" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="148" spans="45:45">
+      <c r="AS148" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="149" spans="45:45">
+      <c r="AS149" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="150" spans="45:45">
+      <c r="AS150" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="151" spans="45:45">
+      <c r="AS151" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="152" spans="45:45">
+      <c r="AS152" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="153" spans="45:45">
+      <c r="AS153" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="154" spans="45:45">
+      <c r="AS154" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="155" spans="45:45">
+      <c r="AS155" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="156" spans="45:45">
+      <c r="AS156" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="157" spans="45:45">
+      <c r="AS157" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="158" spans="45:45">
+      <c r="AS158" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="159" spans="45:45">
+      <c r="AS159" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="160" spans="45:45">
+      <c r="AS160" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="161" spans="45:45">
+      <c r="AS161" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="162" spans="45:45">
+      <c r="AS162" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="163" spans="45:45">
+      <c r="AS163" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="164" spans="45:45">
+      <c r="AS164" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="165" spans="45:45">
+      <c r="AS165" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="166" spans="45:45">
+      <c r="AS166" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="167" spans="45:45">
+      <c r="AS167" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="168" spans="45:45">
+      <c r="AS168" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="169" spans="45:45">
+      <c r="AS169" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="170" spans="45:45">
+      <c r="AS170" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="171" spans="45:45">
+      <c r="AS171" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="172" spans="45:45">
+      <c r="AS172" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="173" spans="45:45">
+      <c r="AS173" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="174" spans="45:45">
+      <c r="AS174" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="175" spans="45:45">
+      <c r="AS175" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="176" spans="45:45">
+      <c r="AS176" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="177" spans="45:45">
+      <c r="AS177" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="178" spans="45:45">
+      <c r="AS178" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="179" spans="45:45">
+      <c r="AS179" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="180" spans="45:45">
+      <c r="AS180" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="181" spans="45:45">
+      <c r="AS181" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="182" spans="45:45">
+      <c r="AS182" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="183" spans="45:45">
+      <c r="AS183" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="184" spans="45:45">
+      <c r="AS184" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="185" spans="45:45">
+      <c r="AS185" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="186" spans="45:45">
+      <c r="AS186" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="187" spans="45:45">
+      <c r="AS187" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="188" spans="45:45">
+      <c r="AS188" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="189" spans="45:45">
+      <c r="AS189" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="190" spans="45:45">
+      <c r="AS190" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="191" spans="45:45">
+      <c r="AS191" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="192" spans="45:45">
+      <c r="AS192" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="193" spans="45:45">
+      <c r="AS193" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="194" spans="45:45">
+      <c r="AS194" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="195" spans="45:45">
+      <c r="AS195" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="196" spans="45:45">
+      <c r="AS196" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="197" spans="45:45">
+      <c r="AS197" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="198" spans="45:45">
+      <c r="AS198" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="199" spans="45:45">
+      <c r="AS199" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="200" spans="45:45">
+      <c r="AS200" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="201" spans="45:45">
+      <c r="AS201" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="202" spans="45:45">
+      <c r="AS202" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="203" spans="45:45">
+      <c r="AS203" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="204" spans="45:45">
+      <c r="AS204" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="205" spans="45:45">
+      <c r="AS205" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="206" spans="45:45">
+      <c r="AS206" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="207" spans="45:45">
+      <c r="AS207" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="208" spans="45:45">
+      <c r="AS208" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="209" spans="45:45">
+      <c r="AS209" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="210" spans="45:45">
+      <c r="AS210" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="211" spans="45:45">
+      <c r="AS211" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="212" spans="45:45">
+      <c r="AS212" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="213" spans="45:45">
+      <c r="AS213" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="214" spans="45:45">
+      <c r="AS214" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="215" spans="45:45">
+      <c r="AS215" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="216" spans="45:45">
+      <c r="AS216" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="217" spans="45:45">
+      <c r="AS217" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="218" spans="45:45">
+      <c r="AS218" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="219" spans="45:45">
+      <c r="AS219" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="220" spans="45:45">
+      <c r="AS220" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="221" spans="45:45">
+      <c r="AS221" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="222" spans="45:45">
+      <c r="AS222" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="223" spans="45:45">
+      <c r="AS223" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="224" spans="45:45">
+      <c r="AS224" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="225" spans="45:45">
+      <c r="AS225" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="226" spans="45:45">
+      <c r="AS226" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="227" spans="45:45">
+      <c r="AS227" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="228" spans="45:45">
+      <c r="AS228" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="229" spans="45:45">
+      <c r="AS229" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="230" spans="45:45">
+      <c r="AS230" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="231" spans="45:45">
+      <c r="AS231" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="232" spans="45:45">
+      <c r="AS232" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="233" spans="45:45">
+      <c r="AS233" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="234" spans="45:45">
+      <c r="AS234" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="235" spans="45:45">
+      <c r="AS235" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="236" spans="45:45">
+      <c r="AS236" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="237" spans="45:45">
+      <c r="AS237" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="238" spans="45:45">
+      <c r="AS238" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="239" spans="45:45">
+      <c r="AS239" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="240" spans="45:45">
+      <c r="AS240" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="241" spans="45:45">
+      <c r="AS241" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="242" spans="45:45">
+      <c r="AS242" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="243" spans="45:45">
+      <c r="AS243" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="244" spans="45:45">
+      <c r="AS244" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="245" spans="45:45">
+      <c r="AS245" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="246" spans="45:45">
+      <c r="AS246" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="247" spans="45:45">
+      <c r="AS247" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="248" spans="45:45">
+      <c r="AS248" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="249" spans="45:45">
+      <c r="AS249" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="250" spans="45:45">
+      <c r="AS250" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="251" spans="45:45">
+      <c r="AS251" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="252" spans="45:45">
+      <c r="AS252" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="253" spans="45:45">
+      <c r="AS253" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="254" spans="45:45">
+      <c r="AS254" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="255" spans="45:45">
+      <c r="AS255" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="256" spans="45:45">
+      <c r="AS256" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="257" spans="45:45">
+      <c r="AS257" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="258" spans="45:45">
+      <c r="AS258" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="259" spans="45:45">
+      <c r="AS259" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="260" spans="45:45">
+      <c r="AS260" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="261" spans="45:45">
+      <c r="AS261" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="262" spans="45:45">
+      <c r="AS262" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="263" spans="45:45">
+      <c r="AS263" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="264" spans="45:45">
+      <c r="AS264" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="265" spans="45:45">
+      <c r="AS265" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="266" spans="45:45">
+      <c r="AS266" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="267" spans="45:45">
+      <c r="AS267" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="268" spans="45:45">
+      <c r="AS268" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="269" spans="45:45">
+      <c r="AS269" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="270" spans="45:45">
+      <c r="AS270" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="271" spans="45:45">
+      <c r="AS271" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="272" spans="45:45">
+      <c r="AS272" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="273" spans="45:45">
+      <c r="AS273" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="274" spans="45:45">
+      <c r="AS274" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="275" spans="45:45">
+      <c r="AS275" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="276" spans="45:45">
+      <c r="AS276" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="277" spans="45:45">
+      <c r="AS277" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="278" spans="45:45">
+      <c r="AS278" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="279" spans="45:45">
+      <c r="AS279" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="280" spans="45:45">
+      <c r="AS280" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="281" spans="45:45">
+      <c r="AS281" t="s">
         <v>681</v>
       </c>
-      <c r="CZ4" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="5" spans="6:104">
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I5" t="s">
-        <v>319</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>403</v>
-      </c>
-      <c r="BL5" t="s">
+    </row>
+    <row r="282" spans="45:45">
+      <c r="AS282" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="6" spans="6:104">
-      <c r="F6" t="s">
-        <v>279</v>
-      </c>
-      <c r="I6" t="s">
-        <v>320</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>404</v>
-      </c>
-      <c r="BL6" t="s">
+    <row r="283" spans="45:45">
+      <c r="AS283" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="7" spans="6:104">
-      <c r="F7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I7" t="s">
-        <v>321</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>405</v>
-      </c>
-      <c r="BL7" t="s">
+    <row r="284" spans="45:45">
+      <c r="AS284" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="8" spans="6:104">
-      <c r="F8" t="s">
-        <v>281</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>406</v>
-      </c>
-      <c r="BL8" t="s">
+    <row r="285" spans="45:45">
+      <c r="AS285" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="9" spans="6:104">
-      <c r="F9" t="s">
-        <v>282</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>407</v>
-      </c>
-      <c r="BL9" t="s">
+    <row r="286" spans="45:45">
+      <c r="AS286" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="10" spans="6:104">
-      <c r="F10" t="s">
-        <v>283</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>408</v>
-      </c>
-      <c r="BL10" t="s">
+    <row r="287" spans="45:45">
+      <c r="AS287" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="11" spans="6:104">
-      <c r="F11" t="s">
-        <v>284</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>409</v>
-      </c>
-      <c r="BL11" t="s">
+    <row r="288" spans="45:45">
+      <c r="AS288" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="12" spans="6:104">
-      <c r="F12" t="s">
-        <v>285</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>410</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="13" spans="6:104">
-      <c r="F13" t="s">
-        <v>286</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>411</v>
-      </c>
-      <c r="BL13" t="s">
+    <row r="289" spans="45:45">
+      <c r="AS289" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="14" spans="6:104">
-      <c r="F14" t="s">
-        <v>287</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>412</v>
-      </c>
-      <c r="BL14" t="s">
+    <row r="290" spans="45:45">
+      <c r="AS290" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="15" spans="6:104">
-      <c r="F15" t="s">
-        <v>288</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>413</v>
-      </c>
-      <c r="BL15" t="s">
+    <row r="291" spans="45:45">
+      <c r="AS291" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="16" spans="6:104">
-      <c r="F16" t="s">
-        <v>289</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>414</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="6:64">
-      <c r="F17" t="s">
-        <v>290</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>415</v>
-      </c>
-      <c r="BL17" t="s">
+    <row r="292" spans="45:45">
+      <c r="AS292" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="18" spans="6:64">
-      <c r="F18" t="s">
-        <v>291</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="6:64">
-      <c r="F19" t="s">
-        <v>292</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="20" spans="6:64">
-      <c r="F20" t="s">
-        <v>293</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="21" spans="6:64">
-      <c r="F21" t="s">
-        <v>294</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="22" spans="6:64">
-      <c r="F22" t="s">
-        <v>295</v>
-      </c>
-      <c r="AR22" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="23" spans="6:64">
-      <c r="F23" t="s">
-        <v>296</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" spans="6:64">
-      <c r="F24" t="s">
-        <v>297</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="25" spans="6:64">
-      <c r="F25" t="s">
-        <v>298</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="26" spans="6:64">
-      <c r="F26" t="s">
-        <v>299</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="27" spans="6:64">
-      <c r="F27" t="s">
-        <v>300</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="28" spans="6:64">
-      <c r="F28" t="s">
-        <v>301</v>
-      </c>
-      <c r="AR28" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="29" spans="6:64">
-      <c r="F29" t="s">
-        <v>302</v>
-      </c>
-      <c r="AR29" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="30" spans="6:64">
-      <c r="F30" t="s">
-        <v>303</v>
-      </c>
-      <c r="AR30" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="31" spans="6:64">
-      <c r="AR31" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="32" spans="6:64">
-      <c r="AR32" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="33" spans="44:44">
-      <c r="AR33" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="34" spans="44:44">
-      <c r="AR34" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="35" spans="44:44">
-      <c r="AR35" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="36" spans="44:44">
-      <c r="AR36" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="37" spans="44:44">
-      <c r="AR37" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="38" spans="44:44">
-      <c r="AR38" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="39" spans="44:44">
-      <c r="AR39" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="40" spans="44:44">
-      <c r="AR40" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="41" spans="44:44">
-      <c r="AR41" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="42" spans="44:44">
-      <c r="AR42" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="43" spans="44:44">
-      <c r="AR43" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="44" spans="44:44">
-      <c r="AR44" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="45" spans="44:44">
-      <c r="AR45" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="46" spans="44:44">
-      <c r="AR46" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="47" spans="44:44">
-      <c r="AR47" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="48" spans="44:44">
-      <c r="AR48" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="49" spans="44:44">
-      <c r="AR49" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="50" spans="44:44">
-      <c r="AR50" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="51" spans="44:44">
-      <c r="AR51" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="52" spans="44:44">
-      <c r="AR52" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="53" spans="44:44">
-      <c r="AR53" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="54" spans="44:44">
-      <c r="AR54" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="55" spans="44:44">
-      <c r="AR55" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="56" spans="44:44">
-      <c r="AR56" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="57" spans="44:44">
-      <c r="AR57" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="58" spans="44:44">
-      <c r="AR58" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="59" spans="44:44">
-      <c r="AR59" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="60" spans="44:44">
-      <c r="AR60" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="61" spans="44:44">
-      <c r="AR61" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="62" spans="44:44">
-      <c r="AR62" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="63" spans="44:44">
-      <c r="AR63" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="64" spans="44:44">
-      <c r="AR64" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="65" spans="44:44">
-      <c r="AR65" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="66" spans="44:44">
-      <c r="AR66" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="67" spans="44:44">
-      <c r="AR67" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="68" spans="44:44">
-      <c r="AR68" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="69" spans="44:44">
-      <c r="AR69" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="70" spans="44:44">
-      <c r="AR70" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="71" spans="44:44">
-      <c r="AR71" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="72" spans="44:44">
-      <c r="AR72" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="73" spans="44:44">
-      <c r="AR73" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="74" spans="44:44">
-      <c r="AR74" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="75" spans="44:44">
-      <c r="AR75" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="76" spans="44:44">
-      <c r="AR76" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="77" spans="44:44">
-      <c r="AR77" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="78" spans="44:44">
-      <c r="AR78" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="79" spans="44:44">
-      <c r="AR79" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="80" spans="44:44">
-      <c r="AR80" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="81" spans="44:44">
-      <c r="AR81" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="82" spans="44:44">
-      <c r="AR82" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="83" spans="44:44">
-      <c r="AR83" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="84" spans="44:44">
-      <c r="AR84" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="85" spans="44:44">
-      <c r="AR85" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="86" spans="44:44">
-      <c r="AR86" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="87" spans="44:44">
-      <c r="AR87" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="88" spans="44:44">
-      <c r="AR88" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="89" spans="44:44">
-      <c r="AR89" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="90" spans="44:44">
-      <c r="AR90" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="91" spans="44:44">
-      <c r="AR91" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="92" spans="44:44">
-      <c r="AR92" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="93" spans="44:44">
-      <c r="AR93" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="94" spans="44:44">
-      <c r="AR94" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="95" spans="44:44">
-      <c r="AR95" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="96" spans="44:44">
-      <c r="AR96" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="97" spans="44:44">
-      <c r="AR97" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="98" spans="44:44">
-      <c r="AR98" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="99" spans="44:44">
-      <c r="AR99" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="100" spans="44:44">
-      <c r="AR100" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="101" spans="44:44">
-      <c r="AR101" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="102" spans="44:44">
-      <c r="AR102" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="103" spans="44:44">
-      <c r="AR103" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="104" spans="44:44">
-      <c r="AR104" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="105" spans="44:44">
-      <c r="AR105" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="106" spans="44:44">
-      <c r="AR106" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="107" spans="44:44">
-      <c r="AR107" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="108" spans="44:44">
-      <c r="AR108" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="109" spans="44:44">
-      <c r="AR109" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="110" spans="44:44">
-      <c r="AR110" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="111" spans="44:44">
-      <c r="AR111" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="112" spans="44:44">
-      <c r="AR112" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="113" spans="44:44">
-      <c r="AR113" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="114" spans="44:44">
-      <c r="AR114" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="115" spans="44:44">
-      <c r="AR115" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="116" spans="44:44">
-      <c r="AR116" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="117" spans="44:44">
-      <c r="AR117" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="118" spans="44:44">
-      <c r="AR118" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="119" spans="44:44">
-      <c r="AR119" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="120" spans="44:44">
-      <c r="AR120" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="121" spans="44:44">
-      <c r="AR121" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="122" spans="44:44">
-      <c r="AR122" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="123" spans="44:44">
-      <c r="AR123" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="124" spans="44:44">
-      <c r="AR124" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="125" spans="44:44">
-      <c r="AR125" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="126" spans="44:44">
-      <c r="AR126" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="127" spans="44:44">
-      <c r="AR127" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="128" spans="44:44">
-      <c r="AR128" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="129" spans="44:44">
-      <c r="AR129" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="130" spans="44:44">
-      <c r="AR130" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="131" spans="44:44">
-      <c r="AR131" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="132" spans="44:44">
-      <c r="AR132" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="133" spans="44:44">
-      <c r="AR133" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="134" spans="44:44">
-      <c r="AR134" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="135" spans="44:44">
-      <c r="AR135" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="136" spans="44:44">
-      <c r="AR136" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="137" spans="44:44">
-      <c r="AR137" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="138" spans="44:44">
-      <c r="AR138" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="139" spans="44:44">
-      <c r="AR139" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="140" spans="44:44">
-      <c r="AR140" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="141" spans="44:44">
-      <c r="AR141" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="142" spans="44:44">
-      <c r="AR142" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="143" spans="44:44">
-      <c r="AR143" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="144" spans="44:44">
-      <c r="AR144" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="145" spans="44:44">
-      <c r="AR145" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="146" spans="44:44">
-      <c r="AR146" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="147" spans="44:44">
-      <c r="AR147" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="148" spans="44:44">
-      <c r="AR148" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="149" spans="44:44">
-      <c r="AR149" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="150" spans="44:44">
-      <c r="AR150" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="151" spans="44:44">
-      <c r="AR151" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="152" spans="44:44">
-      <c r="AR152" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="153" spans="44:44">
-      <c r="AR153" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="154" spans="44:44">
-      <c r="AR154" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="155" spans="44:44">
-      <c r="AR155" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="156" spans="44:44">
-      <c r="AR156" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="157" spans="44:44">
-      <c r="AR157" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="158" spans="44:44">
-      <c r="AR158" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="159" spans="44:44">
-      <c r="AR159" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="160" spans="44:44">
-      <c r="AR160" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="161" spans="44:44">
-      <c r="AR161" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="162" spans="44:44">
-      <c r="AR162" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="163" spans="44:44">
-      <c r="AR163" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="164" spans="44:44">
-      <c r="AR164" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="165" spans="44:44">
-      <c r="AR165" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="166" spans="44:44">
-      <c r="AR166" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="167" spans="44:44">
-      <c r="AR167" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="168" spans="44:44">
-      <c r="AR168" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="169" spans="44:44">
-      <c r="AR169" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="170" spans="44:44">
-      <c r="AR170" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="171" spans="44:44">
-      <c r="AR171" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="172" spans="44:44">
-      <c r="AR172" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="173" spans="44:44">
-      <c r="AR173" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="174" spans="44:44">
-      <c r="AR174" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="175" spans="44:44">
-      <c r="AR175" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="176" spans="44:44">
-      <c r="AR176" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="177" spans="44:44">
-      <c r="AR177" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="178" spans="44:44">
-      <c r="AR178" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="179" spans="44:44">
-      <c r="AR179" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="180" spans="44:44">
-      <c r="AR180" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="181" spans="44:44">
-      <c r="AR181" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="182" spans="44:44">
-      <c r="AR182" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="183" spans="44:44">
-      <c r="AR183" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="184" spans="44:44">
-      <c r="AR184" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="185" spans="44:44">
-      <c r="AR185" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="186" spans="44:44">
-      <c r="AR186" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="187" spans="44:44">
-      <c r="AR187" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="188" spans="44:44">
-      <c r="AR188" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="189" spans="44:44">
-      <c r="AR189" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="190" spans="44:44">
-      <c r="AR190" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="191" spans="44:44">
-      <c r="AR191" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="192" spans="44:44">
-      <c r="AR192" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="193" spans="44:44">
-      <c r="AR193" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="194" spans="44:44">
-      <c r="AR194" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="195" spans="44:44">
-      <c r="AR195" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="196" spans="44:44">
-      <c r="AR196" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="197" spans="44:44">
-      <c r="AR197" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="198" spans="44:44">
-      <c r="AR198" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="199" spans="44:44">
-      <c r="AR199" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="200" spans="44:44">
-      <c r="AR200" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="201" spans="44:44">
-      <c r="AR201" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="202" spans="44:44">
-      <c r="AR202" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="203" spans="44:44">
-      <c r="AR203" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="204" spans="44:44">
-      <c r="AR204" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="205" spans="44:44">
-      <c r="AR205" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="206" spans="44:44">
-      <c r="AR206" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="207" spans="44:44">
-      <c r="AR207" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="208" spans="44:44">
-      <c r="AR208" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="209" spans="44:44">
-      <c r="AR209" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="210" spans="44:44">
-      <c r="AR210" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="211" spans="44:44">
-      <c r="AR211" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="212" spans="44:44">
-      <c r="AR212" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="213" spans="44:44">
-      <c r="AR213" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="214" spans="44:44">
-      <c r="AR214" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="215" spans="44:44">
-      <c r="AR215" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="216" spans="44:44">
-      <c r="AR216" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="217" spans="44:44">
-      <c r="AR217" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="218" spans="44:44">
-      <c r="AR218" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="219" spans="44:44">
-      <c r="AR219" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="220" spans="44:44">
-      <c r="AR220" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="221" spans="44:44">
-      <c r="AR221" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="222" spans="44:44">
-      <c r="AR222" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="223" spans="44:44">
-      <c r="AR223" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="224" spans="44:44">
-      <c r="AR224" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="225" spans="44:44">
-      <c r="AR225" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="226" spans="44:44">
-      <c r="AR226" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="227" spans="44:44">
-      <c r="AR227" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="228" spans="44:44">
-      <c r="AR228" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="229" spans="44:44">
-      <c r="AR229" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="230" spans="44:44">
-      <c r="AR230" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="231" spans="44:44">
-      <c r="AR231" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="232" spans="44:44">
-      <c r="AR232" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="233" spans="44:44">
-      <c r="AR233" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="234" spans="44:44">
-      <c r="AR234" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="235" spans="44:44">
-      <c r="AR235" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="236" spans="44:44">
-      <c r="AR236" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="237" spans="44:44">
-      <c r="AR237" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="238" spans="44:44">
-      <c r="AR238" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="239" spans="44:44">
-      <c r="AR239" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="240" spans="44:44">
-      <c r="AR240" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="241" spans="44:44">
-      <c r="AR241" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="242" spans="44:44">
-      <c r="AR242" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="243" spans="44:44">
-      <c r="AR243" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="244" spans="44:44">
-      <c r="AR244" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="245" spans="44:44">
-      <c r="AR245" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="246" spans="44:44">
-      <c r="AR246" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="247" spans="44:44">
-      <c r="AR247" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="248" spans="44:44">
-      <c r="AR248" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="249" spans="44:44">
-      <c r="AR249" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="250" spans="44:44">
-      <c r="AR250" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="251" spans="44:44">
-      <c r="AR251" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="252" spans="44:44">
-      <c r="AR252" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="253" spans="44:44">
-      <c r="AR253" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="254" spans="44:44">
-      <c r="AR254" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="255" spans="44:44">
-      <c r="AR255" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="256" spans="44:44">
-      <c r="AR256" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="257" spans="44:44">
-      <c r="AR257" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="258" spans="44:44">
-      <c r="AR258" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="259" spans="44:44">
-      <c r="AR259" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="260" spans="44:44">
-      <c r="AR260" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="261" spans="44:44">
-      <c r="AR261" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="262" spans="44:44">
-      <c r="AR262" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="263" spans="44:44">
-      <c r="AR263" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="264" spans="44:44">
-      <c r="AR264" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="265" spans="44:44">
-      <c r="AR265" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="266" spans="44:44">
-      <c r="AR266" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="267" spans="44:44">
-      <c r="AR267" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="268" spans="44:44">
-      <c r="AR268" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="269" spans="44:44">
-      <c r="AR269" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="270" spans="44:44">
-      <c r="AR270" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="271" spans="44:44">
-      <c r="AR271" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="272" spans="44:44">
-      <c r="AR272" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="273" spans="44:44">
-      <c r="AR273" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="274" spans="44:44">
-      <c r="AR274" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="275" spans="44:44">
-      <c r="AR275" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="276" spans="44:44">
-      <c r="AR276" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="277" spans="44:44">
-      <c r="AR277" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="278" spans="44:44">
-      <c r="AR278" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="279" spans="44:44">
-      <c r="AR279" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="280" spans="44:44">
-      <c r="AR280" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="281" spans="44:44">
-      <c r="AR281" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="282" spans="44:44">
-      <c r="AR282" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="283" spans="44:44">
-      <c r="AR283" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="284" spans="44:44">
-      <c r="AR284" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="285" spans="44:44">
-      <c r="AR285" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="286" spans="44:44">
-      <c r="AR286" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="287" spans="44:44">
-      <c r="AR287" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="288" spans="44:44">
-      <c r="AR288" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="289" spans="44:44">
-      <c r="AR289" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="290" spans="44:44">
-      <c r="AR290" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="291" spans="44:44">
-      <c r="AR291" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="292" spans="44:44">
-      <c r="AR292" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="293" spans="44:44">
-      <c r="AR293" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="294" spans="44:44">
-      <c r="AR294" t="s">
-        <v>692</v>
+    <row r="293" spans="45:45">
+      <c r="AS293" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="294" spans="45:45">
+      <c r="AS294" t="s">
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$294</definedName>
     <definedName name="hostsex">'cv_sample'!$BM$1:$BM$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$H$1:$H$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$R$1:$R$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$J$1:$J$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AA$1:$AA$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$DA$1:$DA$4</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="853">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1450,9 +1456,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1471,6 +1474,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1672,6 +1678,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1681,9 +1690,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1723,7 +1729,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1792,6 +1798,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1867,6 +1876,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1888,6 +1900,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1933,6 +1948,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1945,6 +1963,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1954,9 +1975,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1981,6 +1999,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2041,10 +2062,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3102,10 +3123,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3146,10 +3167,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +3197,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3193,7 +3214,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3210,7 +3231,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3227,7 +3248,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3244,7 +3265,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3261,7 +3282,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3278,7 +3299,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3295,7 +3316,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3312,7 +3333,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3329,7 +3350,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3343,7 +3364,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3357,7 +3378,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3371,7 +3392,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3385,7 +3406,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3399,7 +3420,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3413,7 +3434,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3427,7 +3448,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3441,7 +3462,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3451,8 +3472,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3463,7 +3487,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3474,7 +3498,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3485,7 +3509,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3496,7 +3520,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3507,7 +3531,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3518,7 +3542,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3529,7 +3553,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3540,7 +3564,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3551,7 +3575,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3562,7 +3586,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3573,7 +3597,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3584,7 +3608,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3595,7 +3619,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3603,7 +3627,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3611,7 +3635,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3619,7 +3643,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3627,7 +3651,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3635,7 +3659,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3643,7 +3667,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3651,7 +3675,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3659,7 +3683,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3675,236 +3699,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3926,27 +3955,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3966,122 +3995,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4105,714 +4134,714 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:119" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -4851,249 +4880,249 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:DA289"/>
+  <dimension ref="G1:DA294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:105">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="R1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AE1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AS1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BM1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="DA1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="2" spans="7:105">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AE2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AS2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BM2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="DA2" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="7:105">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AS3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BM3" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="DA3" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="4" spans="7:105">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AS4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BM4" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="DA4" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5" spans="7:105">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AS5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BM5" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="7:105">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AS6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BM6" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="7:105">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AS7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BM7" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8" spans="7:105">
       <c r="G8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AS8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BM8" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="7:105">
       <c r="G9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AS9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BM9" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="7:105">
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AS10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="BM10" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="7:105">
       <c r="G11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AS11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="BM11" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" spans="7:105">
       <c r="G12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AS12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BM12" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="7:105">
       <c r="G13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AS13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BM13" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="14" spans="7:105">
       <c r="G14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AS14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="BM14" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" spans="7:105">
       <c r="G15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AS15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="BM15" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="16" spans="7:105">
       <c r="G16" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AS16" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BM16" t="s">
         <v>116</v>
@@ -5101,1412 +5130,1437 @@
     </row>
     <row r="17" spans="7:65">
       <c r="G17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AS17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="BM17" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" spans="7:65">
       <c r="G18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AS18" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="7:65">
       <c r="G19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AS19" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="7:65">
       <c r="G20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AS20" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="7:65">
       <c r="G21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AS21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="7:65">
       <c r="G22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AS22" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="7:65">
       <c r="G23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AS23" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="7:65">
       <c r="G24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AS24" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="7:65">
       <c r="G25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AS25" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="7:65">
       <c r="G26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AS26" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="7:65">
       <c r="G27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AS27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="7:65">
       <c r="G28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AS28" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="7:65">
       <c r="G29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AS29" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="7:65">
       <c r="G30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AS30" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" spans="7:65">
       <c r="AS31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="7:65">
       <c r="AS32" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="45:45">
       <c r="AS33" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="45:45">
       <c r="AS34" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="45:45">
       <c r="AS35" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="45:45">
       <c r="AS36" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="45:45">
       <c r="AS37" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="45:45">
       <c r="AS38" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="45:45">
       <c r="AS39" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="40" spans="45:45">
       <c r="AS40" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="41" spans="45:45">
       <c r="AS41" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="42" spans="45:45">
       <c r="AS42" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" spans="45:45">
       <c r="AS43" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="45:45">
       <c r="AS44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="45:45">
       <c r="AS45" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="45:45">
       <c r="AS46" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="45:45">
       <c r="AS47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="45:45">
       <c r="AS48" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="45:45">
       <c r="AS49" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="50" spans="45:45">
       <c r="AS50" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51" spans="45:45">
       <c r="AS51" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="45:45">
       <c r="AS52" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="45:45">
       <c r="AS53" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54" spans="45:45">
       <c r="AS54" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" spans="45:45">
       <c r="AS55" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="45:45">
       <c r="AS56" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="45:45">
       <c r="AS57" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" spans="45:45">
       <c r="AS58" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="45:45">
       <c r="AS59" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" spans="45:45">
       <c r="AS60" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" spans="45:45">
       <c r="AS61" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="45:45">
       <c r="AS62" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="63" spans="45:45">
       <c r="AS63" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="45:45">
       <c r="AS64" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" spans="45:45">
       <c r="AS65" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="45:45">
       <c r="AS66" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="67" spans="45:45">
       <c r="AS67" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="45:45">
       <c r="AS68" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="45:45">
       <c r="AS69" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" spans="45:45">
       <c r="AS70" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="45:45">
       <c r="AS71" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="72" spans="45:45">
       <c r="AS72" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="73" spans="45:45">
       <c r="AS73" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="74" spans="45:45">
       <c r="AS74" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="45:45">
       <c r="AS75" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="76" spans="45:45">
       <c r="AS76" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="77" spans="45:45">
       <c r="AS77" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="78" spans="45:45">
       <c r="AS78" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79" spans="45:45">
       <c r="AS79" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="80" spans="45:45">
       <c r="AS80" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81" spans="45:45">
       <c r="AS81" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="82" spans="45:45">
       <c r="AS82" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="83" spans="45:45">
       <c r="AS83" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="84" spans="45:45">
       <c r="AS84" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85" spans="45:45">
       <c r="AS85" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="86" spans="45:45">
       <c r="AS86" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="45:45">
       <c r="AS87" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="88" spans="45:45">
       <c r="AS88" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="89" spans="45:45">
       <c r="AS89" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" spans="45:45">
       <c r="AS90" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="91" spans="45:45">
       <c r="AS91" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="92" spans="45:45">
       <c r="AS92" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="93" spans="45:45">
       <c r="AS93" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="94" spans="45:45">
       <c r="AS94" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="95" spans="45:45">
       <c r="AS95" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="96" spans="45:45">
       <c r="AS96" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="97" spans="45:45">
       <c r="AS97" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="98" spans="45:45">
       <c r="AS98" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="99" spans="45:45">
       <c r="AS99" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="45:45">
       <c r="AS100" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="45:45">
       <c r="AS101" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="102" spans="45:45">
       <c r="AS102" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="103" spans="45:45">
       <c r="AS103" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104" spans="45:45">
       <c r="AS104" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="105" spans="45:45">
       <c r="AS105" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="45:45">
       <c r="AS106" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="107" spans="45:45">
       <c r="AS107" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="108" spans="45:45">
       <c r="AS108" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" spans="45:45">
       <c r="AS109" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="110" spans="45:45">
       <c r="AS110" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" spans="45:45">
       <c r="AS111" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="112" spans="45:45">
       <c r="AS112" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="113" spans="45:45">
       <c r="AS113" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="114" spans="45:45">
       <c r="AS114" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="115" spans="45:45">
       <c r="AS115" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="116" spans="45:45">
       <c r="AS116" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="117" spans="45:45">
       <c r="AS117" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="118" spans="45:45">
       <c r="AS118" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="119" spans="45:45">
       <c r="AS119" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="120" spans="45:45">
       <c r="AS120" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="121" spans="45:45">
       <c r="AS121" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="122" spans="45:45">
       <c r="AS122" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="123" spans="45:45">
       <c r="AS123" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="124" spans="45:45">
       <c r="AS124" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="125" spans="45:45">
       <c r="AS125" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="126" spans="45:45">
       <c r="AS126" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="127" spans="45:45">
       <c r="AS127" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="128" spans="45:45">
       <c r="AS128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129" spans="45:45">
       <c r="AS129" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="130" spans="45:45">
       <c r="AS130" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="131" spans="45:45">
       <c r="AS131" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="132" spans="45:45">
       <c r="AS132" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="133" spans="45:45">
       <c r="AS133" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="134" spans="45:45">
       <c r="AS134" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="135" spans="45:45">
       <c r="AS135" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="136" spans="45:45">
       <c r="AS136" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="137" spans="45:45">
       <c r="AS137" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="45:45">
       <c r="AS138" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="139" spans="45:45">
       <c r="AS139" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="140" spans="45:45">
       <c r="AS140" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="141" spans="45:45">
       <c r="AS141" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="142" spans="45:45">
       <c r="AS142" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="143" spans="45:45">
       <c r="AS143" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="144" spans="45:45">
       <c r="AS144" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="145" spans="45:45">
       <c r="AS145" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" spans="45:45">
       <c r="AS146" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="147" spans="45:45">
       <c r="AS147" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="148" spans="45:45">
       <c r="AS148" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="149" spans="45:45">
       <c r="AS149" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="150" spans="45:45">
       <c r="AS150" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="151" spans="45:45">
       <c r="AS151" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="152" spans="45:45">
       <c r="AS152" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="45:45">
       <c r="AS153" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="154" spans="45:45">
       <c r="AS154" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="155" spans="45:45">
       <c r="AS155" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="156" spans="45:45">
       <c r="AS156" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="157" spans="45:45">
       <c r="AS157" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="158" spans="45:45">
       <c r="AS158" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="159" spans="45:45">
       <c r="AS159" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="160" spans="45:45">
       <c r="AS160" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="161" spans="45:45">
       <c r="AS161" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="162" spans="45:45">
       <c r="AS162" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="163" spans="45:45">
       <c r="AS163" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="164" spans="45:45">
       <c r="AS164" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="165" spans="45:45">
       <c r="AS165" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="166" spans="45:45">
       <c r="AS166" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="167" spans="45:45">
       <c r="AS167" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="168" spans="45:45">
       <c r="AS168" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="169" spans="45:45">
       <c r="AS169" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170" spans="45:45">
       <c r="AS170" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="171" spans="45:45">
       <c r="AS171" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="172" spans="45:45">
       <c r="AS172" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="173" spans="45:45">
       <c r="AS173" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="174" spans="45:45">
       <c r="AS174" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="175" spans="45:45">
       <c r="AS175" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="176" spans="45:45">
       <c r="AS176" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" spans="45:45">
       <c r="AS177" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="178" spans="45:45">
       <c r="AS178" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="179" spans="45:45">
       <c r="AS179" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="180" spans="45:45">
       <c r="AS180" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="181" spans="45:45">
       <c r="AS181" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="182" spans="45:45">
       <c r="AS182" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="183" spans="45:45">
       <c r="AS183" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="184" spans="45:45">
       <c r="AS184" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="185" spans="45:45">
       <c r="AS185" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="186" spans="45:45">
       <c r="AS186" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="187" spans="45:45">
       <c r="AS187" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="188" spans="45:45">
       <c r="AS188" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="189" spans="45:45">
       <c r="AS189" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="190" spans="45:45">
       <c r="AS190" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="191" spans="45:45">
       <c r="AS191" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="192" spans="45:45">
       <c r="AS192" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="193" spans="45:45">
       <c r="AS193" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="194" spans="45:45">
       <c r="AS194" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="195" spans="45:45">
       <c r="AS195" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="196" spans="45:45">
       <c r="AS196" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="197" spans="45:45">
       <c r="AS197" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="198" spans="45:45">
       <c r="AS198" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="199" spans="45:45">
       <c r="AS199" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="200" spans="45:45">
       <c r="AS200" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="201" spans="45:45">
       <c r="AS201" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="202" spans="45:45">
       <c r="AS202" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="203" spans="45:45">
       <c r="AS203" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="204" spans="45:45">
       <c r="AS204" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="205" spans="45:45">
       <c r="AS205" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="206" spans="45:45">
       <c r="AS206" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="207" spans="45:45">
       <c r="AS207" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="208" spans="45:45">
       <c r="AS208" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="209" spans="45:45">
       <c r="AS209" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="45:45">
       <c r="AS210" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="211" spans="45:45">
       <c r="AS211" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="212" spans="45:45">
       <c r="AS212" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="213" spans="45:45">
       <c r="AS213" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="214" spans="45:45">
       <c r="AS214" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="215" spans="45:45">
       <c r="AS215" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="216" spans="45:45">
       <c r="AS216" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="217" spans="45:45">
       <c r="AS217" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="218" spans="45:45">
       <c r="AS218" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="219" spans="45:45">
       <c r="AS219" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="220" spans="45:45">
       <c r="AS220" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="221" spans="45:45">
       <c r="AS221" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="222" spans="45:45">
       <c r="AS222" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="223" spans="45:45">
       <c r="AS223" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="224" spans="45:45">
       <c r="AS224" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="225" spans="45:45">
       <c r="AS225" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="226" spans="45:45">
       <c r="AS226" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="227" spans="45:45">
       <c r="AS227" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="228" spans="45:45">
       <c r="AS228" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="229" spans="45:45">
       <c r="AS229" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="230" spans="45:45">
       <c r="AS230" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="231" spans="45:45">
       <c r="AS231" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="232" spans="45:45">
       <c r="AS232" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="233" spans="45:45">
       <c r="AS233" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="234" spans="45:45">
       <c r="AS234" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="235" spans="45:45">
       <c r="AS235" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="236" spans="45:45">
       <c r="AS236" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="237" spans="45:45">
       <c r="AS237" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="238" spans="45:45">
       <c r="AS238" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="239" spans="45:45">
       <c r="AS239" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="240" spans="45:45">
       <c r="AS240" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="241" spans="45:45">
       <c r="AS241" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="242" spans="45:45">
       <c r="AS242" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="243" spans="45:45">
       <c r="AS243" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="244" spans="45:45">
       <c r="AS244" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="245" spans="45:45">
       <c r="AS245" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="246" spans="45:45">
       <c r="AS246" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="247" spans="45:45">
       <c r="AS247" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="248" spans="45:45">
       <c r="AS248" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="249" spans="45:45">
       <c r="AS249" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="250" spans="45:45">
       <c r="AS250" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="251" spans="45:45">
       <c r="AS251" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="252" spans="45:45">
       <c r="AS252" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="253" spans="45:45">
       <c r="AS253" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="254" spans="45:45">
       <c r="AS254" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="255" spans="45:45">
       <c r="AS255" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="256" spans="45:45">
       <c r="AS256" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="257" spans="45:45">
       <c r="AS257" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="258" spans="45:45">
       <c r="AS258" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="259" spans="45:45">
       <c r="AS259" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="260" spans="45:45">
       <c r="AS260" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="261" spans="45:45">
       <c r="AS261" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="262" spans="45:45">
       <c r="AS262" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="263" spans="45:45">
       <c r="AS263" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="264" spans="45:45">
       <c r="AS264" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="265" spans="45:45">
       <c r="AS265" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="266" spans="45:45">
       <c r="AS266" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="267" spans="45:45">
       <c r="AS267" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="268" spans="45:45">
       <c r="AS268" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="269" spans="45:45">
       <c r="AS269" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="270" spans="45:45">
       <c r="AS270" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="271" spans="45:45">
       <c r="AS271" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="272" spans="45:45">
       <c r="AS272" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="273" spans="45:45">
       <c r="AS273" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="274" spans="45:45">
       <c r="AS274" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="275" spans="45:45">
       <c r="AS275" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="276" spans="45:45">
       <c r="AS276" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="277" spans="45:45">
       <c r="AS277" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="278" spans="45:45">
       <c r="AS278" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="279" spans="45:45">
       <c r="AS279" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="280" spans="45:45">
       <c r="AS280" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="281" spans="45:45">
       <c r="AS281" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="282" spans="45:45">
       <c r="AS282" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="283" spans="45:45">
       <c r="AS283" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="284" spans="45:45">
       <c r="AS284" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="285" spans="45:45">
       <c r="AS285" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="286" spans="45:45">
       <c r="AS286" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="287" spans="45:45">
       <c r="AS287" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="288" spans="45:45">
       <c r="AS288" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="289" spans="45:45">
       <c r="AS289" t="s">
-        <v>687</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="290" spans="45:45">
+      <c r="AS290" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="291" spans="45:45">
+      <c r="AS291" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="292" spans="45:45">
+      <c r="AS292" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="293" spans="45:45">
+      <c r="AS293" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="294" spans="45:45">
+      <c r="AS294" t="s">
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -2272,7 +2272,7 @@
     <t>host of the symbiotic host subject id</t>
   </si>
   <si>
-    <t>(Optional) A unique identifier by which each host of the symbiotic host organism subject can be referred to, de-identified, e.g. #h14. (Units: year)</t>
+    <t>(Optional) A unique identifier by which each host of the symbiotic host organism subject can be referred to, de-identified, e.g. #h14.</t>
   </si>
   <si>
     <t>host of the symbiotic host taxon id</t>
@@ -2362,31 +2362,31 @@
     <t>host cellular location</t>
   </si>
   <si>
-    <t>(Recommended) The localization of the symbiotic host organism within the host from which it was sampled: e.g. intracellular if the symbiotic host organism is localized within the cells or extracellular if the symbiotic host organism is localized outside of cells. (Units: %)</t>
+    <t>(Recommended) The localization of the symbiotic host organism within the host from which it was sampled: e.g. intracellular if the symbiotic host organism is localized within the cells or extracellular if the symbiotic host organism is localized outside of cells.</t>
   </si>
   <si>
     <t>host of the symbiotic host infra-specific rank</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic rank information about the host of the symbiotic host organism below subspecies level, such as variety, form, rank etc. (Units: °C)</t>
+    <t>(Optional) Taxonomic rank information about the host of the symbiotic host organism below subspecies level, such as variety, form, rank etc.</t>
   </si>
   <si>
     <t>type of symbiosis</t>
   </si>
   <si>
-    <t>(Recommended) Type of biological interaction established between the symbiotic host organism being sampled and its respective host (Units: °C)</t>
+    <t>(Recommended) Type of biological interaction established between the symbiotic host organism being sampled and its respective host</t>
   </si>
   <si>
     <t>observed coinfecting organisms in host of host</t>
   </si>
   <si>
-    <t>(Optional) The taxonomic name of any coinfecting organism observed in a symbiotic relationship with the host of the sampled host organism. e.g. where a sample collected from a host trematode species (a) which was collected from a host_of_host fish (b) that was also infected with a nematode (c), the value here would be (c) the nematode {species name} or {common name}. multiple co-infecting species may be added in a comma-separated list. for listing symbiotic organisms associated with the host (a) use the term observed host symbiont. (Units: year)</t>
+    <t>(Optional) The taxonomic name of any coinfecting organism observed in a symbiotic relationship with the host of the sampled host organism. e.g. where a sample collected from a host trematode species (a) which was collected from a host_of_host fish (b) that was also infected with a nematode (c), the value here would be (c) the nematode {species name} or {common name}. multiple co-infecting species may be added in a comma-separated list. for listing symbiotic organisms associated with the host (a) use the term observed host symbiont.</t>
   </si>
   <si>
     <t>host of the symbiotic host infra-specific name</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic name information of the host of the symbiotic host organism below subspecies level. (Units: year)</t>
+    <t>(Optional) Taxonomic name information of the host of the symbiotic host organism below subspecies level.</t>
   </si>
   <si>
     <t>host of the symbiotic host total mass</t>
@@ -2398,25 +2398,25 @@
     <t>host of the symbiotic host local environmental context</t>
   </si>
   <si>
-    <t>(Optional) For a symbiotic host organism the local anatomical environment within its host may have causal influences. report the anatomical entity(s) which are in the direct environment of the symbiotic host organism being sampled and which you believe have significant causal influences on your sample or specimen. for example, if the symbiotic host organism being sampled is an intestinal worm, its local environmental context will be the term for intestine from uberon (http://uberon.github.io/). (Units: g/m3)</t>
+    <t>(Optional) For a symbiotic host organism the local anatomical environment within its host may have causal influences. report the anatomical entity(s) which are in the direct environment of the symbiotic host organism being sampled and which you believe have significant causal influences on your sample or specimen. for example, if the symbiotic host organism being sampled is an intestinal worm, its local environmental context will be the term for intestine from uberon (http://uberon.github.io/).</t>
   </si>
   <si>
     <t>host of the symbiotic host common name</t>
   </si>
   <si>
-    <t>(Optional) Common name of the host of the symbiotic host organism. (Units: °C)</t>
+    <t>(Optional) Common name of the host of the symbiotic host organism.</t>
   </si>
   <si>
     <t>host of the symbiotic host genotype</t>
   </si>
   <si>
-    <t>(Optional) Observed genotype of the host of the symbiotic host organism. (Units: year)</t>
+    <t>(Optional) Observed genotype of the host of the symbiotic host organism.</t>
   </si>
   <si>
     <t>route of transmission</t>
   </si>
   <si>
-    <t>(Optional) Description of path taken by the symbiotic host organism being sampled in order to establish a symbiotic relationship with the host (with which it was observed at the time of sampling) via a mode of transmission (specified in mode_transmission). (Units: mm)</t>
+    <t>(Optional) Description of path taken by the symbiotic host organism being sampled in order to establish a symbiotic relationship with the host (with which it was observed at the time of sampling) via a mode of transmission (specified in mode_transmission).</t>
   </si>
   <si>
     <t>host dry mass</t>

--- a/templates/ERC000057/metadata_template_ERC000057.xlsx
+++ b/templates/ERC000057/metadata_template_ERC000057.xlsx
@@ -20,7 +20,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$294</definedName>
     <definedName name="hostsex">'cv_sample'!$BM$1:$BM$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="854">
   <si>
     <t>alias</t>
   </si>
@@ -734,6 +734,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3126,7 +3129,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3170,7 +3173,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3197,7 +3200,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3934,6 +3937,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3955,27 +3963,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3995,122 +4003,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4134,714 +4142,714 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="2" spans="1:119" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -4885,244 +4893,244 @@
   <sheetData>
     <row r="1" spans="7:105">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AE1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AS1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="BM1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="DA1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2" spans="7:105">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AE2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AS2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="BM2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="DA2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="3" spans="7:105">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BM3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="DA3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" spans="7:105">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AS4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BM4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="DA4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" spans="7:105">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AS5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="BM5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" spans="7:105">
       <c r="G6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AS6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="BM6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="7:105">
       <c r="G7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AS7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="BM7" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="7:105">
       <c r="G8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AS8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="BM8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="7:105">
       <c r="G9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AS9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="BM9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="7:105">
       <c r="G10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AS10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="BM10" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11" spans="7:105">
       <c r="G11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="BM11" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="12" spans="7:105">
       <c r="G12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BM12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="13" spans="7:105">
       <c r="G13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AS13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="BM13" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14" spans="7:105">
       <c r="G14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AS14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="BM14" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15" spans="7:105">
       <c r="G15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AS15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="BM15" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" spans="7:105">
       <c r="G16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AS16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="BM16" t="s">
         <v>116</v>
@@ -5130,1437 +5138,1437 @@
     </row>
     <row r="17" spans="7:65">
       <c r="G17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AS17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="BM17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="7:65">
       <c r="G18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AS18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="7:65">
       <c r="G19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AS19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="7:65">
       <c r="G20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AS20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="7:65">
       <c r="G21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AS21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="7:65">
       <c r="G22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AS22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="7:65">
       <c r="G23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AS23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="7:65">
       <c r="G24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AS24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="7:65">
       <c r="G25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AS25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="7:65">
       <c r="G26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="7:65">
       <c r="G27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AS27" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="7:65">
       <c r="G28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AS28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="7:65">
       <c r="G29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AS29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="7:65">
       <c r="G30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AS30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="7:65">
       <c r="AS31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="7:65">
       <c r="AS32" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="45:45">
       <c r="AS33" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="45:45">
       <c r="AS34" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="45:45">
       <c r="AS35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="45:45">
       <c r="AS36" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="45:45">
       <c r="AS37" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="45:45">
       <c r="AS38" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="45:45">
       <c r="AS39" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="45:45">
       <c r="AS40" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="41" spans="45:45">
       <c r="AS41" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" spans="45:45">
       <c r="AS42" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="45:45">
       <c r="AS43" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44" spans="45:45">
       <c r="AS44" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="45" spans="45:45">
       <c r="AS45" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="46" spans="45:45">
       <c r="AS46" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="45:45">
       <c r="AS47" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="45:45">
       <c r="AS48" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49" spans="45:45">
       <c r="AS49" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" spans="45:45">
       <c r="AS50" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="45:45">
       <c r="AS51" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" spans="45:45">
       <c r="AS52" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="45:45">
       <c r="AS53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="54" spans="45:45">
       <c r="AS54" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="55" spans="45:45">
       <c r="AS55" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56" spans="45:45">
       <c r="AS56" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="57" spans="45:45">
       <c r="AS57" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="45:45">
       <c r="AS58" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="59" spans="45:45">
       <c r="AS59" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" spans="45:45">
       <c r="AS60" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="61" spans="45:45">
       <c r="AS61" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="62" spans="45:45">
       <c r="AS62" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" spans="45:45">
       <c r="AS63" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="45:45">
       <c r="AS64" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="65" spans="45:45">
       <c r="AS65" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" spans="45:45">
       <c r="AS66" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67" spans="45:45">
       <c r="AS67" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="68" spans="45:45">
       <c r="AS68" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" spans="45:45">
       <c r="AS69" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" spans="45:45">
       <c r="AS70" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" spans="45:45">
       <c r="AS71" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" spans="45:45">
       <c r="AS72" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="73" spans="45:45">
       <c r="AS73" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="74" spans="45:45">
       <c r="AS74" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="75" spans="45:45">
       <c r="AS75" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="76" spans="45:45">
       <c r="AS76" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77" spans="45:45">
       <c r="AS77" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="78" spans="45:45">
       <c r="AS78" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" spans="45:45">
       <c r="AS79" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" spans="45:45">
       <c r="AS80" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="81" spans="45:45">
       <c r="AS81" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="82" spans="45:45">
       <c r="AS82" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="83" spans="45:45">
       <c r="AS83" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" spans="45:45">
       <c r="AS84" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="85" spans="45:45">
       <c r="AS85" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="86" spans="45:45">
       <c r="AS86" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="87" spans="45:45">
       <c r="AS87" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="88" spans="45:45">
       <c r="AS88" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="89" spans="45:45">
       <c r="AS89" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="90" spans="45:45">
       <c r="AS90" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="91" spans="45:45">
       <c r="AS91" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="92" spans="45:45">
       <c r="AS92" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="93" spans="45:45">
       <c r="AS93" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="94" spans="45:45">
       <c r="AS94" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="95" spans="45:45">
       <c r="AS95" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="96" spans="45:45">
       <c r="AS96" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="97" spans="45:45">
       <c r="AS97" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="98" spans="45:45">
       <c r="AS98" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="99" spans="45:45">
       <c r="AS99" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="45:45">
       <c r="AS100" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="101" spans="45:45">
       <c r="AS101" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="102" spans="45:45">
       <c r="AS102" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="103" spans="45:45">
       <c r="AS103" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="104" spans="45:45">
       <c r="AS104" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="105" spans="45:45">
       <c r="AS105" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="106" spans="45:45">
       <c r="AS106" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="107" spans="45:45">
       <c r="AS107" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="108" spans="45:45">
       <c r="AS108" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109" spans="45:45">
       <c r="AS109" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" spans="45:45">
       <c r="AS110" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="111" spans="45:45">
       <c r="AS111" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="112" spans="45:45">
       <c r="AS112" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="113" spans="45:45">
       <c r="AS113" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="114" spans="45:45">
       <c r="AS114" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="115" spans="45:45">
       <c r="AS115" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="116" spans="45:45">
       <c r="AS116" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="117" spans="45:45">
       <c r="AS117" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="118" spans="45:45">
       <c r="AS118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="119" spans="45:45">
       <c r="AS119" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="120" spans="45:45">
       <c r="AS120" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="121" spans="45:45">
       <c r="AS121" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="122" spans="45:45">
       <c r="AS122" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="123" spans="45:45">
       <c r="AS123" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="124" spans="45:45">
       <c r="AS124" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="125" spans="45:45">
       <c r="AS125" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="126" spans="45:45">
       <c r="AS126" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="45:45">
       <c r="AS127" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="128" spans="45:45">
       <c r="AS128" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="129" spans="45:45">
       <c r="AS129" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="130" spans="45:45">
       <c r="AS130" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="131" spans="45:45">
       <c r="AS131" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="132" spans="45:45">
       <c r="AS132" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="133" spans="45:45">
       <c r="AS133" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="134" spans="45:45">
       <c r="AS134" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="135" spans="45:45">
       <c r="AS135" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="136" spans="45:45">
       <c r="AS136" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="137" spans="45:45">
       <c r="AS137" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="138" spans="45:45">
       <c r="AS138" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="139" spans="45:45">
       <c r="AS139" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140" spans="45:45">
       <c r="AS140" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="141" spans="45:45">
       <c r="AS141" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="142" spans="45:45">
       <c r="AS142" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="143" spans="45:45">
       <c r="AS143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="144" spans="45:45">
       <c r="AS144" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="145" spans="45:45">
       <c r="AS145" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="146" spans="45:45">
       <c r="AS146" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="147" spans="45:45">
       <c r="AS147" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="148" spans="45:45">
       <c r="AS148" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="149" spans="45:45">
       <c r="AS149" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="150" spans="45:45">
       <c r="AS150" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="151" spans="45:45">
       <c r="AS151" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="152" spans="45:45">
       <c r="AS152" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="153" spans="45:45">
       <c r="AS153" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="154" spans="45:45">
       <c r="AS154" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="155" spans="45:45">
       <c r="AS155" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="156" spans="45:45">
       <c r="AS156" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="157" spans="45:45">
       <c r="AS157" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="158" spans="45:45">
       <c r="AS158" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="159" spans="45:45">
       <c r="AS159" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="160" spans="45:45">
       <c r="AS160" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="161" spans="45:45">
       <c r="AS161" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="162" spans="45:45">
       <c r="AS162" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="163" spans="45:45">
       <c r="AS163" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="164" spans="45:45">
       <c r="AS164" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="165" spans="45:45">
       <c r="AS165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="166" spans="45:45">
       <c r="AS166" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="167" spans="45:45">
       <c r="AS167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="168" spans="45:45">
       <c r="AS168" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="45:45">
       <c r="AS169" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="170" spans="45:45">
       <c r="AS170" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="171" spans="45:45">
       <c r="AS171" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="172" spans="45:45">
       <c r="AS172" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="173" spans="45:45">
       <c r="AS173" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="174" spans="45:45">
       <c r="AS174" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="175" spans="45:45">
       <c r="AS175" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="176" spans="45:45">
       <c r="AS176" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="177" spans="45:45">
       <c r="AS177" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="178" spans="45:45">
       <c r="AS178" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="179" spans="45:45">
       <c r="AS179" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="180" spans="45:45">
       <c r="AS180" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="181" spans="45:45">
       <c r="AS181" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="182" spans="45:45">
       <c r="AS182" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="183" spans="45:45">
       <c r="AS183" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="184" spans="45:45">
       <c r="AS184" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="185" spans="45:45">
       <c r="AS185" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="186" spans="45:45">
       <c r="AS186" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="187" spans="45:45">
       <c r="AS187" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="188" spans="45:45">
       <c r="AS188" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="189" spans="45:45">
       <c r="AS189" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="190" spans="45:45">
       <c r="AS190" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="191" spans="45:45">
       <c r="AS191" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="192" spans="45:45">
       <c r="AS192" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="193" spans="45:45">
       <c r="AS193" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="194" spans="45:45">
       <c r="AS194" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="195" spans="45:45">
       <c r="AS195" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="196" spans="45:45">
       <c r="AS196" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="197" spans="45:45">
       <c r="AS197" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="198" spans="45:45">
       <c r="AS198" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="199" spans="45:45">
       <c r="AS199" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="200" spans="45:45">
       <c r="AS200" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="201" spans="45:45">
       <c r="AS201" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="202" spans="45:45">
       <c r="AS202" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="203" spans="45:45">
       <c r="AS203" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="204" spans="45:45">
       <c r="AS204" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="205" spans="45:45">
       <c r="AS205" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="206" spans="45:45">
       <c r="AS206" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="207" spans="45:45">
       <c r="AS207" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="208" spans="45:45">
       <c r="AS208" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="209" spans="45:45">
       <c r="AS209" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="210" spans="45:45">
       <c r="AS210" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="211" spans="45:45">
       <c r="AS211" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="212" spans="45:45">
       <c r="AS212" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="213" spans="45:45">
       <c r="AS213" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="45:45">
       <c r="AS214" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="215" spans="45:45">
       <c r="AS215" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="216" spans="45:45">
       <c r="AS216" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="217" spans="45:45">
       <c r="AS217" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="218" spans="45:45">
       <c r="AS218" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="219" spans="45:45">
       <c r="AS219" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="220" spans="45:45">
       <c r="AS220" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="221" spans="45:45">
       <c r="AS221" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="222" spans="45:45">
       <c r="AS222" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="223" spans="45:45">
       <c r="AS223" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="224" spans="45:45">
       <c r="AS224" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="225" spans="45:45">
       <c r="AS225" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="226" spans="45:45">
       <c r="AS226" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="227" spans="45:45">
       <c r="AS227" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="228" spans="45:45">
       <c r="AS228" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="229" spans="45:45">
       <c r="AS229" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="230" spans="45:45">
       <c r="AS230" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="231" spans="45:45">
       <c r="AS231" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="232" spans="45:45">
       <c r="AS232" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="233" spans="45:45">
       <c r="AS233" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="234" spans="45:45">
       <c r="AS234" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="235" spans="45:45">
       <c r="AS235" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="236" spans="45:45">
       <c r="AS236" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="237" spans="45:45">
       <c r="AS237" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="238" spans="45:45">
       <c r="AS238" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="239" spans="45:45">
       <c r="AS239" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="240" spans="45:45">
       <c r="AS240" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="241" spans="45:45">
       <c r="AS241" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="242" spans="45:45">
       <c r="AS242" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="243" spans="45:45">
       <c r="AS243" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="244" spans="45:45">
       <c r="AS244" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="245" spans="45:45">
       <c r="AS245" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="246" spans="45:45">
       <c r="AS246" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="247" spans="45:45">
       <c r="AS247" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="248" spans="45:45">
       <c r="AS248" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="249" spans="45:45">
       <c r="AS249" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="250" spans="45:45">
       <c r="AS250" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="251" spans="45:45">
       <c r="AS251" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="252" spans="45:45">
       <c r="AS252" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="253" spans="45:45">
       <c r="AS253" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="254" spans="45:45">
       <c r="AS254" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="255" spans="45:45">
       <c r="AS255" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="256" spans="45:45">
       <c r="AS256" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="257" spans="45:45">
       <c r="AS257" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="258" spans="45:45">
       <c r="AS258" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="259" spans="45:45">
       <c r="AS259" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="260" spans="45:45">
       <c r="AS260" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="261" spans="45:45">
       <c r="AS261" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="262" spans="45:45">
       <c r="AS262" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="263" spans="45:45">
       <c r="AS263" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="264" spans="45:45">
       <c r="AS264" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="265" spans="45:45">
       <c r="AS265" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="266" spans="45:45">
       <c r="AS266" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="267" spans="45:45">
       <c r="AS267" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="268" spans="45:45">
       <c r="AS268" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="269" spans="45:45">
       <c r="AS269" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="270" spans="45:45">
       <c r="AS270" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="271" spans="45:45">
       <c r="AS271" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="272" spans="45:45">
       <c r="AS272" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="273" spans="45:45">
       <c r="AS273" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="274" spans="45:45">
       <c r="AS274" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="275" spans="45:45">
       <c r="AS275" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="276" spans="45:45">
       <c r="AS276" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="277" spans="45:45">
       <c r="AS277" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="278" spans="45:45">
       <c r="AS278" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="279" spans="45:45">
       <c r="AS279" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="280" spans="45:45">
       <c r="AS280" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="281" spans="45:45">
       <c r="AS281" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="282" spans="45:45">
       <c r="AS282" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="283" spans="45:45">
       <c r="AS283" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="284" spans="45:45">
       <c r="AS284" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="285" spans="45:45">
       <c r="AS285" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="286" spans="45:45">
       <c r="AS286" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="287" spans="45:45">
       <c r="AS287" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="288" spans="45:45">
       <c r="AS288" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="289" spans="45:45">
       <c r="AS289" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="290" spans="45:45">
       <c r="AS290" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="291" spans="45:45">
       <c r="AS291" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="292" spans="45:45">
       <c r="AS292" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="293" spans="45:45">
       <c r="AS293" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="294" spans="45:45">
       <c r="AS294" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
